--- a/VT_REG1_ELC_V12.xlsx
+++ b/VT_REG1_ELC_V12.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
-  <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F285464-C26D-4EE5-8AAA-6C1B248B09E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" tabRatio="901" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="EB1" sheetId="133" r:id="rId1"/>
-    <sheet name="RES_ELC" sheetId="152" r:id="rId2"/>
-    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId3"/>
-    <sheet name="Con_ELC" sheetId="143" r:id="rId4"/>
-    <sheet name="Emi" sheetId="149" r:id="rId5"/>
+    <sheet name="EB1" sheetId="133" r:id="rId3"/>
+    <sheet name="RES_ELC" sheetId="152" r:id="rId4"/>
+    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId5"/>
+    <sheet name="Con_ELC" sheetId="143" r:id="rId6"/>
+    <sheet name="Emi" sheetId="149" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -38,20 +37,19 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -63,7 +61,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -72,7 +69,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -83,7 +79,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -92,7 +87,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -103,7 +97,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -112,7 +105,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -123,7 +115,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -132,7 +123,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -143,7 +133,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -152,7 +141,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -160,13 +148,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0">
+    <comment ref="O3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -175,7 +162,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -186,12 +172,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0">
+    <comment ref="P3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -201,7 +186,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -211,7 +195,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -221,7 +204,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -231,7 +213,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -241,7 +222,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -251,7 +231,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -259,12 +238,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0">
+    <comment ref="Q3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -274,7 +252,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -284,7 +261,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -294,7 +270,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -304,7 +279,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -312,12 +286,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0">
+    <comment ref="R3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -328,7 +301,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -337,7 +309,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -345,12 +316,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="2" shapeId="0">
+    <comment ref="P15" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -361,7 +331,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -370,7 +339,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -381,7 +349,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -390,7 +357,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -401,7 +367,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -410,7 +375,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -421,7 +385,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -430,7 +393,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -438,13 +400,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="1" shapeId="0">
+    <comment ref="Q15" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -453,7 +414,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -463,12 +423,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="2" shapeId="0">
+    <comment ref="R15" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -478,7 +437,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -488,7 +446,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -498,7 +455,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -507,7 +463,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -517,7 +472,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -526,12 +480,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="2" shapeId="0">
+    <comment ref="J16" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -540,7 +493,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -551,7 +503,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -561,7 +512,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -571,7 +521,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -581,7 +530,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -591,7 +539,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -601,7 +548,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -611,7 +557,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -621,7 +566,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -631,7 +575,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -641,7 +584,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -651,7 +593,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -661,7 +602,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -671,7 +611,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -681,7 +620,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -692,7 +630,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -701,7 +638,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -711,7 +647,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -721,7 +656,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -731,7 +665,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -741,7 +674,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -751,7 +683,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -761,7 +692,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -773,20 +703,19 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -798,7 +727,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -807,7 +735,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -818,7 +745,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -827,7 +753,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -838,7 +763,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -847,7 +771,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -858,7 +781,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -867,7 +789,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -878,7 +799,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -887,7 +807,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -895,13 +814,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="1" shapeId="0">
+    <comment ref="Y3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -910,7 +828,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -921,12 +838,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="2" shapeId="0">
+    <comment ref="Z3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -936,7 +852,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -946,7 +861,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -956,7 +870,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -966,7 +879,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -976,7 +888,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -986,7 +897,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -994,12 +904,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="2" shapeId="0">
+    <comment ref="AA3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1009,7 +918,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1019,7 +927,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1029,7 +936,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1039,7 +945,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1047,12 +952,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="2" shapeId="0">
+    <comment ref="AB3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1063,7 +967,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1072,7 +975,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1080,12 +982,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="2" shapeId="0">
+    <comment ref="Z9" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1096,7 +997,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1105,7 +1005,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1116,7 +1015,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1125,7 +1023,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1136,7 +1033,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1145,7 +1041,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1156,7 +1051,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1165,7 +1059,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1173,13 +1066,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="1" shapeId="0">
+    <comment ref="AA9" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1188,7 +1080,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1198,12 +1089,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="2" shapeId="0">
+    <comment ref="AB9" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1213,7 +1103,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1223,7 +1112,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1233,7 +1121,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1242,7 +1129,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1252,7 +1138,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1261,12 +1146,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="T10" authorId="2" shapeId="0">
+    <comment ref="T10" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1275,7 +1159,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1286,7 +1169,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1296,7 +1178,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1306,7 +1187,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1316,7 +1196,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1326,7 +1205,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1336,7 +1214,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1346,7 +1223,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1356,7 +1232,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1366,7 +1241,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1376,7 +1250,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1386,7 +1259,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1396,7 +1268,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1406,7 +1277,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1416,7 +1286,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1427,7 +1296,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1436,7 +1304,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1446,7 +1313,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1456,7 +1322,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1466,7 +1331,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1476,7 +1340,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1486,7 +1349,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1496,7 +1358,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -2027,14 +1888,17 @@
     <numFmt numFmtId="190" formatCode="0.0000"/>
     <numFmt numFmtId="195" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2048,11 +1912,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="12"/>
@@ -2061,40 +1920,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -2116,19 +1947,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2209,12 +2031,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
@@ -2224,7 +2040,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="9" tint="-0.249977111117893"/>
+      <color theme="9" tint="-0.249970003962517"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2252,7 +2068,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2264,80 +2134,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2346,173 +2167,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2530,7 +2184,64 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -2540,27 +2251,25 @@
         <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2568,260 +2277,456 @@
         <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
     </border>
   </borders>
-  <cellStyleXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="48">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="11" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="22" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="0" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="5" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="20" fillId="7" borderId="6" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="0" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="6" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="187" fontId="13" fillId="5" borderId="7" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="17" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="8" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="18" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="9" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="19" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="10" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="4" fillId="16" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="9" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="26" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="3" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2829,57 +2734,133 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="30">
-    <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
-    <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
-    <cellStyle name="Accent2" xfId="3" builtinId="33"/>
-    <cellStyle name="Calculation" xfId="4" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="5"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Input" xfId="7" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
+  <cellStyles count="34">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="9"/>
-    <cellStyle name="Normal 2" xfId="10"/>
-    <cellStyle name="Normal 4" xfId="11"/>
-    <cellStyle name="Normal 4 2" xfId="12"/>
-    <cellStyle name="Normal 8" xfId="13"/>
-    <cellStyle name="Normal 9 2" xfId="14"/>
-    <cellStyle name="Normale_B2020" xfId="15"/>
-    <cellStyle name="Percent" xfId="16" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="17"/>
-    <cellStyle name="Percent 3" xfId="18"/>
-    <cellStyle name="Percent 3 2" xfId="19"/>
-    <cellStyle name="Percent 3 3" xfId="20"/>
-    <cellStyle name="Percent 3 4" xfId="21"/>
-    <cellStyle name="Percent 4" xfId="22"/>
-    <cellStyle name="Percent 4 2" xfId="23"/>
-    <cellStyle name="Percent 4 3" xfId="24"/>
-    <cellStyle name="Percent 4 4" xfId="25"/>
-    <cellStyle name="Percent 5" xfId="26"/>
-    <cellStyle name="Percent 6" xfId="27"/>
-    <cellStyle name="Percent 7" xfId="28"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="29"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="20% - Accent5" xfId="20" builtinId="46"/>
+    <cellStyle name="40% - Accent3" xfId="21" builtinId="39"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
+    <cellStyle name="Calculation" xfId="23" builtinId="22"/>
+    <cellStyle name="Comma 2" xfId="24"/>
+    <cellStyle name="Good" xfId="25" builtinId="26"/>
+    <cellStyle name="Input" xfId="26" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="27" builtinId="28"/>
+    <cellStyle name="Normal 10" xfId="28"/>
+    <cellStyle name="Normal 2" xfId="29"/>
+    <cellStyle name="Normal 4" xfId="30"/>
+    <cellStyle name="Normal 4 2" xfId="31"/>
+    <cellStyle name="Normal 8" xfId="32"/>
+    <cellStyle name="Normal 9 2" xfId="33"/>
+    <cellStyle name="Normale_B2020" xfId="34"/>
+    <cellStyle name="Percent 2" xfId="35"/>
+    <cellStyle name="Percent 3" xfId="36"/>
+    <cellStyle name="Percent 3 2" xfId="37"/>
+    <cellStyle name="Percent 3 3" xfId="38"/>
+    <cellStyle name="Percent 3 4" xfId="39"/>
+    <cellStyle name="Percent 4" xfId="40"/>
+    <cellStyle name="Percent 4 2" xfId="41"/>
+    <cellStyle name="Percent 4 3" xfId="42"/>
+    <cellStyle name="Percent 4 4" xfId="43"/>
+    <cellStyle name="Percent 5" xfId="44"/>
+    <cellStyle name="Percent 6" xfId="45"/>
+    <cellStyle name="Percent 7" xfId="46"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="47"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2892,7 +2873,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2911,7 +2892,7 @@
         <xdr:cNvPr id="56975" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07B54768-2264-459D-AAAF-4E7CAD4688C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07b54768-2264-459d-aaaf-4e7cad4688c6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2920,14 +2901,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2937,9 +2917,7 @@
           <a:off x="123825" y="962025"/>
           <a:ext cx="800100" cy="2238375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -2985,7 +2963,7 @@
         <xdr:cNvPr id="56976" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998F4-DAF5-4AB5-A34B-DFA9CC7FF7F7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998f4-daf5-4ab5-a34b-dfa9cc7ff7f7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2994,14 +2972,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3011,9 +2988,7 @@
           <a:off x="1552575" y="18926175"/>
           <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3059,7 +3034,7 @@
         <xdr:cNvPr id="56977" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD288841-D70D-4C2E-9A6A-06C46B032C2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ad288841-d70d-4c2e-9a6a-06c46b032c2b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3068,14 +3043,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3085,9 +3059,7 @@
           <a:off x="1552575" y="1104900"/>
           <a:ext cx="6524625" cy="3905250"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3133,7 +3105,7 @@
         <xdr:cNvPr id="56978" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7EDBE9C-2FFC-4928-AE9B-DF9BBBDE5C06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f7edbe9c-2ffc-4928-ae9b-df9bbbde5c06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3142,14 +3114,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3159,9 +3130,7 @@
           <a:off x="1552575" y="4962525"/>
           <a:ext cx="3343275" cy="952500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3193,7 +3162,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3207,12 +3176,12 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6B2F145-8850-4388-9ADE-B2C38CEC5F7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f6b2f145-8850-4388-9ade-b2c38cec5f7b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3220,12 +3189,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6537960" y="4933949"/>
-          <a:ext cx="6376035" cy="981075"/>
+          <a:off x="6534150" y="4933950"/>
+          <a:ext cx="6372225" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3234,7 +3201,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3242,16 +3209,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3262,7 +3229,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3274,7 +3241,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3286,7 +3253,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3300,7 +3267,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3313,7 +3280,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3325,7 +3292,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3336,7 +3303,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3352,7 +3319,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
@@ -3366,12 +3333,12 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>1090</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D1CAE3-AB1F-44E7-83A8-8CFE9F3A6676}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32d1cae3-ab1f-44e7-83a8-8cfe9f3a6676}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3379,12 +3346,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10692974" y="4231428"/>
-          <a:ext cx="6483756" cy="1262412"/>
+          <a:off x="12925425" y="4276725"/>
+          <a:ext cx="6477000" cy="1285875"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3393,7 +3358,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3401,16 +3366,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3421,7 +3386,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3433,7 +3398,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3445,7 +3410,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3459,7 +3424,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3472,7 +3437,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3490,7 +3455,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3504,12 +3469,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1A3727-B21E-4010-995E-8645C474E6C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bd1a3727-b21e-4010-995e-8645c474e6c5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3517,12 +3482,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1971675"/>
+          <a:off x="609600" y="2143125"/>
           <a:ext cx="4391025" cy="552450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3531,7 +3494,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3539,16 +3502,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3559,7 +3522,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3571,7 +3534,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3582,7 +3545,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3598,7 +3561,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -3733,7 +3696,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -3746,28 +3709,28 @@
       <sheetData sheetId="1">
         <row r="10">
           <cell r="D10">
-            <v>-37.464700000000001</v>
+            <v>-37.4647</v>
           </cell>
           <cell r="E10">
-            <v>-317.19200000000001</v>
+            <v>-317.192</v>
           </cell>
           <cell r="F10">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>-16.283999999999999</v>
+            <v>-16.284</v>
           </cell>
           <cell r="H10">
-            <v>-2.1499999999999998E-2</v>
+            <v>-0.0215</v>
           </cell>
           <cell r="I10">
-            <v>-528.76099999999997</v>
+            <v>-528.761</v>
           </cell>
           <cell r="J10">
-            <v>-164.50800000000001</v>
+            <v>-164.508</v>
           </cell>
           <cell r="K10">
-            <v>-0.61599999999999999</v>
+            <v>-0.616</v>
           </cell>
           <cell r="L10">
             <v>-205.88</v>
@@ -3800,27 +3763,27 @@
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>-1274.6994499999998</v>
+            <v>-1274.69945</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>-6238.7780000000012</v>
+            <v>-6238.778</v>
           </cell>
           <cell r="E11">
-            <v>-2254.2175999999999</v>
+            <v>-2254.2176</v>
           </cell>
           <cell r="F11">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>-30.160499999999999</v>
+            <v>-30.1605</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>-23.835000000000001</v>
+            <v>-23.835</v>
           </cell>
           <cell r="J11">
             <v>0</v>
@@ -3832,16 +3795,16 @@
             <v>-524.78</v>
           </cell>
           <cell r="M11">
-            <v>-33.529000000000003</v>
+            <v>-33.529</v>
           </cell>
           <cell r="N11">
             <v>-4455</v>
           </cell>
           <cell r="O11">
-            <v>-527.25918750000005</v>
+            <v>-527.2591875</v>
           </cell>
           <cell r="P11">
-            <v>-502.66000000000008</v>
+            <v>-502.66</v>
           </cell>
           <cell r="Q11">
             <v>-263.8965</v>
@@ -3850,16 +3813,16 @@
             <v>-68</v>
           </cell>
           <cell r="S11">
-            <v>-16.474499999999999</v>
+            <v>-16.4745</v>
           </cell>
           <cell r="T11">
-            <v>868.77949999999998</v>
+            <v>868.7795</v>
           </cell>
           <cell r="U11">
             <v>5790.5</v>
           </cell>
           <cell r="V11">
-            <v>-8279.3107875000023</v>
+            <v>-8279.3107875</v>
           </cell>
         </row>
         <row r="12">
@@ -3873,13 +3836,13 @@
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>-7.6189999999999998</v>
+            <v>-7.619</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>-0.23350000000000001</v>
+            <v>-0.2335</v>
           </cell>
           <cell r="J12">
             <v>0</v>
@@ -3909,16 +3872,16 @@
             <v>0</v>
           </cell>
           <cell r="S12">
-            <v>-0.78449999999999998</v>
+            <v>-0.7845</v>
           </cell>
           <cell r="T12">
-            <v>329.37150000000003</v>
+            <v>329.3715</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>-26.820549999999912</v>
+            <v>-26.8205499999999</v>
           </cell>
         </row>
         <row r="13">
@@ -3935,22 +3898,22 @@
             <v>5701.34</v>
           </cell>
           <cell r="H13">
-            <v>969.47799999999995</v>
+            <v>969.478</v>
           </cell>
           <cell r="I13">
-            <v>1086.3040000000001</v>
+            <v>1086.304</v>
           </cell>
           <cell r="J13">
-            <v>3354.9119999999998</v>
+            <v>3354.912</v>
           </cell>
           <cell r="K13">
-            <v>970.28800000000001</v>
+            <v>970.288</v>
           </cell>
           <cell r="L13">
-            <v>2285.1019999999999</v>
+            <v>2285.102</v>
           </cell>
           <cell r="M13">
-            <v>1299.9449999999999</v>
+            <v>1299.945</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -3977,7 +3940,7 @@
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>-200.86150000000021</v>
+            <v>-200.8615</v>
           </cell>
         </row>
       </sheetData>
@@ -4335,29 +4298,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="5" tint="-0.249977111117893"/>
+    <tabColor theme="5" tint="-0.249970003962517"/>
   </sheetPr>
   <dimension ref="A1:AA17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="12.1428571428571" customWidth="1"/>
+    <col min="9" max="12" width="10.8571428571429" customWidth="1"/>
+    <col min="13" max="13" width="17.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.8571428571429" customWidth="1"/>
+    <col min="22" max="22" width="7.28571428571429" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28571428571429" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="24:27" s="6" customFormat="1" ht="12.75">
       <c r="X1" s="23" t="s">
         <v>78</v>
       </c>
@@ -4371,7 +4334,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:27" ht="15.75">
       <c r="C2" s="7"/>
       <c r="D2" s="48" t="s">
         <v>42</v>
@@ -4441,7 +4404,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:22" ht="25.5">
       <c r="C3" s="67" t="s">
         <v>121</v>
       </c>
@@ -4503,7 +4466,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:24" ht="12.75">
       <c r="B4" s="46"/>
       <c r="C4" s="83" t="s">
         <v>55</v>
@@ -4529,7 +4492,7 @@
       <c r="V4" s="84"/>
       <c r="X4" s="6"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:24" ht="12.75">
       <c r="B5" s="50" t="s">
         <v>56</v>
       </c>
@@ -4537,84 +4500,84 @@
         <v>57</v>
       </c>
       <c r="D5" s="51">
-        <f>[2]EB1!D10</f>
+        <f>'[2]EB1'!D10</f>
         <v>-37.464700000000001</v>
       </c>
       <c r="E5" s="51">
-        <f>[2]EB1!E10</f>
+        <f>'[2]EB1'!E10</f>
         <v>-317.19200000000001</v>
       </c>
       <c r="F5" s="51">
-        <f>[2]EB1!F10</f>
+        <f>'[2]EB1'!F10</f>
         <v>0</v>
       </c>
       <c r="G5" s="51">
-        <f>[2]EB1!G10</f>
+        <f>'[2]EB1'!G10</f>
         <v>-16.283999999999999</v>
       </c>
       <c r="H5" s="51">
-        <f>[2]EB1!H10</f>
-        <v>-2.1499999999999998E-2</v>
+        <f>'[2]EB1'!H10</f>
+        <v>-0.021499999999999998</v>
       </c>
       <c r="I5" s="51">
-        <f>[2]EB1!I10</f>
+        <f>'[2]EB1'!I10</f>
         <v>-528.76099999999997</v>
       </c>
       <c r="J5" s="51">
-        <f>[2]EB1!J10</f>
+        <f>'[2]EB1'!J10</f>
         <v>-164.50800000000001</v>
       </c>
       <c r="K5" s="51">
-        <f>[2]EB1!K10</f>
+        <f>'[2]EB1'!K10</f>
         <v>-0.61599999999999999</v>
       </c>
       <c r="L5" s="51">
-        <f>[2]EB1!L10</f>
+        <f>'[2]EB1'!L10</f>
         <v>-205.88</v>
       </c>
       <c r="M5" s="51">
-        <f>[2]EB1!M10</f>
+        <f>'[2]EB1'!M10</f>
         <v>0</v>
       </c>
       <c r="N5" s="51">
-        <f>[2]EB1!N10</f>
+        <f>'[2]EB1'!N10</f>
         <v>0</v>
       </c>
       <c r="O5" s="51">
-        <f>[2]EB1!O10</f>
+        <f>'[2]EB1'!O10</f>
         <v>-3.21225</v>
       </c>
       <c r="P5" s="51">
-        <f>[2]EB1!P10</f>
+        <f>'[2]EB1'!P10</f>
         <v>0</v>
       </c>
       <c r="Q5" s="51">
-        <f>[2]EB1!Q10</f>
+        <f>'[2]EB1'!Q10</f>
         <v>0</v>
       </c>
       <c r="R5" s="51">
-        <f>[2]EB1!R10</f>
+        <f>'[2]EB1'!R10</f>
         <v>0</v>
       </c>
       <c r="S5" s="51">
-        <f>[2]EB1!S10</f>
-        <v>-0.76</v>
+        <f>'[2]EB1'!S10</f>
+        <v>-0.76000000000000001</v>
       </c>
       <c r="T5" s="51">
-        <f>[2]EB1!T10</f>
+        <f>'[2]EB1'!T10</f>
         <v>0</v>
       </c>
       <c r="U5" s="51">
-        <f>[2]EB1!U10</f>
+        <f>'[2]EB1'!U10</f>
         <v>0</v>
       </c>
       <c r="V5" s="85">
-        <f>[2]EB1!V10</f>
+        <f>'[2]EB1'!V10</f>
         <v>-1274.6994499999998</v>
       </c>
       <c r="X5" s="6"/>
     </row>
-    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" ht="15">
       <c r="B6" s="50" t="s">
         <v>48</v>
       </c>
@@ -4622,84 +4585,84 @@
         <v>58</v>
       </c>
       <c r="D6" s="54">
-        <f>[2]EB1!D11</f>
+        <f>'[2]EB1'!D11</f>
         <v>-6238.7780000000012</v>
       </c>
       <c r="E6" s="53">
-        <f>[2]EB1!E11</f>
+        <f>'[2]EB1'!E11</f>
         <v>-2254.2175999999999</v>
       </c>
       <c r="F6" s="53">
-        <f>[2]EB1!F11</f>
+        <f>'[2]EB1'!F11</f>
         <v>0</v>
       </c>
       <c r="G6" s="53">
-        <f>[2]EB1!G11</f>
+        <f>'[2]EB1'!G11</f>
         <v>-30.160499999999999</v>
       </c>
       <c r="H6" s="53">
-        <f>[2]EB1!H11</f>
+        <f>'[2]EB1'!H11</f>
         <v>0</v>
       </c>
       <c r="I6" s="53">
-        <f>[2]EB1!I11</f>
+        <f>'[2]EB1'!I11</f>
         <v>-23.835000000000001</v>
       </c>
       <c r="J6" s="53">
-        <f>[2]EB1!J11</f>
+        <f>'[2]EB1'!J11</f>
         <v>0</v>
       </c>
       <c r="K6" s="53">
-        <f>[2]EB1!K11</f>
+        <f>'[2]EB1'!K11</f>
         <v>0</v>
       </c>
       <c r="L6" s="53">
-        <f>[2]EB1!L11</f>
-        <v>-524.78</v>
+        <f>'[2]EB1'!L11</f>
+        <v>-524.77999999999997</v>
       </c>
       <c r="M6" s="53">
-        <f>[2]EB1!M11</f>
+        <f>'[2]EB1'!M11</f>
         <v>-33.529000000000003</v>
       </c>
       <c r="N6" s="53">
-        <f>[2]EB1!N11</f>
+        <f>'[2]EB1'!N11</f>
         <v>-4455</v>
       </c>
       <c r="O6" s="53">
-        <f>[2]EB1!O11</f>
+        <f>'[2]EB1'!O11</f>
         <v>-527.25918750000005</v>
       </c>
       <c r="P6" s="53">
-        <f>[2]EB1!P11</f>
+        <f>'[2]EB1'!P11</f>
         <v>-502.66000000000008</v>
       </c>
       <c r="Q6" s="53">
-        <f>[2]EB1!Q11</f>
+        <f>'[2]EB1'!Q11</f>
         <v>-263.8965</v>
       </c>
       <c r="R6" s="53">
-        <f>[2]EB1!R11</f>
+        <f>'[2]EB1'!R11</f>
         <v>-68</v>
       </c>
       <c r="S6" s="51">
-        <f>[2]EB1!S11</f>
+        <f>'[2]EB1'!S11</f>
         <v>-16.474499999999999</v>
       </c>
       <c r="T6" s="51">
-        <f>[2]EB1!T11</f>
+        <f>'[2]EB1'!T11</f>
         <v>868.77949999999998</v>
       </c>
       <c r="U6" s="53">
-        <f>[2]EB1!U11</f>
+        <f>'[2]EB1'!U11</f>
         <v>5790.5</v>
       </c>
       <c r="V6" s="85">
-        <f>[2]EB1!V11</f>
+        <f>'[2]EB1'!V11</f>
         <v>-8279.3107875000023</v>
       </c>
       <c r="X6" s="95"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:24" ht="12.75">
       <c r="B7" s="50" t="s">
         <v>59</v>
       </c>
@@ -4707,84 +4670,84 @@
         <v>60</v>
       </c>
       <c r="D7" s="51">
-        <f>[2]EB1!D12</f>
+        <f>'[2]EB1'!D12</f>
         <v>-104.9074</v>
       </c>
       <c r="E7" s="51">
-        <f>[2]EB1!E12</f>
+        <f>'[2]EB1'!E12</f>
         <v>-120.5204</v>
       </c>
       <c r="F7" s="51">
-        <f>[2]EB1!F12</f>
+        <f>'[2]EB1'!F12</f>
         <v>0</v>
       </c>
       <c r="G7" s="51">
-        <f>[2]EB1!G12</f>
+        <f>'[2]EB1'!G12</f>
         <v>-7.6189999999999998</v>
       </c>
       <c r="H7" s="51">
-        <f>[2]EB1!H12</f>
+        <f>'[2]EB1'!H12</f>
         <v>0</v>
       </c>
       <c r="I7" s="51">
-        <f>[2]EB1!I12</f>
+        <f>'[2]EB1'!I12</f>
         <v>-0.23350000000000001</v>
       </c>
       <c r="J7" s="51">
-        <f>[2]EB1!J12</f>
+        <f>'[2]EB1'!J12</f>
         <v>0</v>
       </c>
       <c r="K7" s="51">
-        <f>[2]EB1!K12</f>
+        <f>'[2]EB1'!K12</f>
         <v>0</v>
       </c>
       <c r="L7" s="51">
-        <f>[2]EB1!L12</f>
-        <v>-15.2</v>
+        <f>'[2]EB1'!L12</f>
+        <v>-15.199999999999999</v>
       </c>
       <c r="M7" s="51">
-        <f>[2]EB1!M12</f>
+        <f>'[2]EB1'!M12</f>
         <v>-1.772</v>
       </c>
       <c r="N7" s="51">
-        <f>[2]EB1!N12</f>
+        <f>'[2]EB1'!N12</f>
         <v>0</v>
       </c>
       <c r="O7" s="51">
-        <f>[2]EB1!O12</f>
+        <f>'[2]EB1'!O12</f>
         <v>-105.15525</v>
       </c>
       <c r="P7" s="51">
-        <f>[2]EB1!P12</f>
+        <f>'[2]EB1'!P12</f>
         <v>0</v>
       </c>
       <c r="Q7" s="51">
-        <f>[2]EB1!Q12</f>
+        <f>'[2]EB1'!Q12</f>
         <v>0</v>
       </c>
       <c r="R7" s="51">
-        <f>[2]EB1!R12</f>
+        <f>'[2]EB1'!R12</f>
         <v>0</v>
       </c>
       <c r="S7" s="51">
-        <f>[2]EB1!S12</f>
+        <f>'[2]EB1'!S12</f>
         <v>-0.78449999999999998</v>
       </c>
       <c r="T7" s="51">
-        <f>[2]EB1!T12</f>
+        <f>'[2]EB1'!T12</f>
         <v>329.37150000000003</v>
       </c>
       <c r="U7" s="51">
-        <f>[2]EB1!U12</f>
+        <f>'[2]EB1'!U12</f>
         <v>0</v>
       </c>
       <c r="V7" s="85">
-        <f>[2]EB1!V12</f>
+        <f>'[2]EB1'!V12</f>
         <v>-26.820549999999912</v>
       </c>
       <c r="X7" s="6"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" ht="12.75">
       <c r="B8" s="50" t="s">
         <v>61</v>
       </c>
@@ -4792,83 +4755,83 @@
         <v>62</v>
       </c>
       <c r="D8" s="74">
-        <f>[2]EB1!D13</f>
+        <f>'[2]EB1'!D13</f>
         <v>0</v>
       </c>
       <c r="E8" s="51">
-        <f>[2]EB1!E13</f>
+        <f>'[2]EB1'!E13</f>
         <v>0</v>
       </c>
       <c r="F8" s="51">
-        <f>[2]EB1!F13</f>
+        <f>'[2]EB1'!F13</f>
         <v>-15868.2305</v>
       </c>
       <c r="G8" s="51">
-        <f>[2]EB1!G13</f>
-        <v>5701.34</v>
+        <f>'[2]EB1'!G13</f>
+        <v>5701.3400000000001</v>
       </c>
       <c r="H8" s="51">
-        <f>[2]EB1!H13</f>
+        <f>'[2]EB1'!H13</f>
         <v>969.47799999999995</v>
       </c>
       <c r="I8" s="51">
-        <f>[2]EB1!I13</f>
+        <f>'[2]EB1'!I13</f>
         <v>1086.3040000000001</v>
       </c>
       <c r="J8" s="51">
-        <f>[2]EB1!J13</f>
+        <f>'[2]EB1'!J13</f>
         <v>3354.9119999999998</v>
       </c>
       <c r="K8" s="51">
-        <f>[2]EB1!K13</f>
+        <f>'[2]EB1'!K13</f>
         <v>970.28800000000001</v>
       </c>
       <c r="L8" s="51">
-        <f>[2]EB1!L13</f>
+        <f>'[2]EB1'!L13</f>
         <v>2285.1019999999999</v>
       </c>
       <c r="M8" s="51">
-        <f>[2]EB1!M13</f>
+        <f>'[2]EB1'!M13</f>
         <v>1299.9449999999999</v>
       </c>
       <c r="N8" s="51">
-        <f>[2]EB1!N13</f>
+        <f>'[2]EB1'!N13</f>
         <v>0</v>
       </c>
       <c r="O8" s="51">
-        <f>[2]EB1!O13</f>
+        <f>'[2]EB1'!O13</f>
         <v>0</v>
       </c>
       <c r="P8" s="51">
-        <f>[2]EB1!P13</f>
+        <f>'[2]EB1'!P13</f>
         <v>0</v>
       </c>
       <c r="Q8" s="51">
-        <f>[2]EB1!Q13</f>
+        <f>'[2]EB1'!Q13</f>
         <v>0</v>
       </c>
       <c r="R8" s="51">
-        <f>[2]EB1!R13</f>
+        <f>'[2]EB1'!R13</f>
         <v>0</v>
       </c>
       <c r="S8" s="51">
-        <f>[2]EB1!S13</f>
+        <f>'[2]EB1'!S13</f>
         <v>0</v>
       </c>
       <c r="T8" s="51">
-        <f>[2]EB1!T13</f>
+        <f>'[2]EB1'!T13</f>
         <v>0</v>
       </c>
       <c r="U8" s="51">
-        <f>[2]EB1!U13</f>
+        <f>'[2]EB1'!U13</f>
         <v>0</v>
       </c>
       <c r="V8" s="85">
-        <f>[2]EB1!V13</f>
+        <f>'[2]EB1'!V13</f>
         <v>-200.86150000000021</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" ht="15">
       <c r="B9" s="46"/>
       <c r="C9" s="55" t="s">
         <v>63</v>
@@ -4878,8 +4841,8 @@
         <v>-6381.1501000000017</v>
       </c>
       <c r="E9" s="56">
-        <f t="shared" ref="E9:U9" si="0">SUM(E5:E8)</f>
-        <v>-2691.93</v>
+        <f t="shared" si="0" ref="E9:U9">SUM(E5:E8)</f>
+        <v>-2691.9299999999998</v>
       </c>
       <c r="F9" s="56">
         <f t="shared" si="0"/>
@@ -4950,7 +4913,7 @@
         <v>-9781.6922875000037</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="12.75">
       <c r="A10" s="6"/>
       <c r="D10" s="10"/>
       <c r="F10" s="10"/>
@@ -4962,7 +4925,7 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="12.75">
       <c r="A11" s="6"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -4979,7 +4942,7 @@
       <c r="Q11" s="96"/>
       <c r="R11" s="96"/>
     </row>
-    <row r="12" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" s="6"/>
       <c r="C12" s="53" t="s">
         <v>142</v>
@@ -4995,15 +4958,15 @@
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="12.75">
       <c r="A13" s="6"/>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="12.75">
       <c r="A14" s="6"/>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="12.75">
       <c r="A15" s="6"/>
       <c r="C15" s="64" t="s">
         <v>89</v>
@@ -5016,7 +4979,7 @@
       </c>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="12.75">
       <c r="A16" s="6"/>
       <c r="B16" s="23" t="s">
         <v>98</v>
@@ -5032,7 +4995,7 @@
       </c>
       <c r="V16" s="8"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5" ht="12.75">
       <c r="B17" s="50" t="s">
         <v>48</v>
       </c>
@@ -5044,33 +5007,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:M5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="7.71428571428571" customWidth="1"/>
+    <col min="3" max="4" width="6.85714285714286" customWidth="1"/>
+    <col min="14" max="14" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="5:6" ht="12.75">
       <c r="E1" s="11"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="18">
       <c r="B2" s="78" t="s">
         <v>146</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="4" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="5:13" ht="18">
       <c r="E4" s="119" t="s">
         <v>149</v>
       </c>
@@ -5083,7 +5046,7 @@
       <c r="L4" s="120"/>
       <c r="M4" s="121"/>
     </row>
-    <row r="5" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:13" ht="12.75" customHeight="1">
       <c r="E5" s="79" t="s">
         <v>147</v>
       </c>
@@ -5101,37 +5064,37 @@
     <mergeCell ref="E4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28571428571429" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="2.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="7.14285714285714" customWidth="1"/>
+    <col min="12" max="12" width="14.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
+    <col min="15" max="15" width="10.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15">
       <c r="B1" s="12" t="s">
         <v>65</v>
       </c>
@@ -5152,7 +5115,7 @@
       </c>
       <c r="H1" s="39"/>
     </row>
-    <row r="2" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="31.5">
       <c r="B2" s="14" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -5188,7 +5151,7 @@
       <c r="Q2" s="107"/>
       <c r="R2" s="107"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="10:18" ht="12.75">
       <c r="J3" s="108" t="s">
         <v>7</v>
       </c>
@@ -5217,7 +5180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1">
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -5251,7 +5214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" ht="12.75">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -5272,7 +5235,7 @@
         <v>Electricity Plants Solid Fuels</v>
       </c>
       <c r="N5" s="111" t="str">
-        <f t="shared" ref="N5:N12" si="0">$E$2</f>
+        <f t="shared" si="0" ref="N5:N12">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O5" s="111"/>
@@ -5280,7 +5243,7 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="111"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" ht="12.75">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -5307,7 +5270,7 @@
       <c r="Q6" s="111"/>
       <c r="R6" s="111"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:18" ht="12.75">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -5334,7 +5297,7 @@
       <c r="Q7" s="111"/>
       <c r="R7" s="111"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" ht="12.75">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -5361,7 +5324,7 @@
       <c r="Q8" s="111"/>
       <c r="R8" s="111"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" ht="12.75">
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -5388,7 +5351,7 @@
       <c r="Q9" s="111"/>
       <c r="R9" s="111"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:18" ht="12.75">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -5415,7 +5378,7 @@
       <c r="Q10" s="111"/>
       <c r="R10" s="111"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" ht="12.75">
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -5442,7 +5405,7 @@
       <c r="Q11" s="111"/>
       <c r="R11" s="111"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" ht="12.75">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -5469,11 +5432,11 @@
       <c r="Q12" s="111"/>
       <c r="R12" s="111"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="12:13" ht="12.75">
       <c r="L13" s="27"/>
       <c r="M13" s="29"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:18" ht="12.75">
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
@@ -5491,7 +5454,7 @@
       <c r="Q14" s="113"/>
       <c r="R14" s="113"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:18" ht="12.75">
       <c r="B15" s="20" t="s">
         <v>1</v>
       </c>
@@ -5541,7 +5504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" ht="23.25" thickBot="1">
       <c r="B16" s="19" t="s">
         <v>37</v>
       </c>
@@ -5591,7 +5554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" ht="13.5" thickBot="1">
       <c r="B17" s="18" t="s">
         <v>76</v>
       </c>
@@ -5618,7 +5581,7 @@
       <c r="Q17" s="114"/>
       <c r="R17" s="114"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" ht="12.75">
       <c r="B18" s="25" t="str">
         <f>Sector_Fuels_ELC!L18</f>
         <v>FTE-ELCCOA</v>
@@ -5644,26 +5607,26 @@
       </c>
       <c r="K18" s="116"/>
       <c r="L18" s="111" t="str">
-        <f t="shared" ref="L18:L25" si="1">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <f t="shared" si="1" ref="L18:L25">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-ELCCOA</v>
       </c>
       <c r="M18" s="112" t="str">
-        <f t="shared" ref="M18:M25" si="2">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <f t="shared" si="2" ref="M18:M25">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
       <c r="N18" s="111" t="str">
-        <f t="shared" ref="N18:N25" si="3">$E$2</f>
+        <f t="shared" si="3" ref="N18:N25">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O18" s="111" t="str">
-        <f t="shared" ref="O18:O25" si="4">$E$2&amp;"a"</f>
+        <f t="shared" si="4" ref="O18:O25">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P18" s="111"/>
       <c r="Q18" s="111"/>
       <c r="R18" s="111"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" ht="12.75">
       <c r="B19" s="25" t="str">
         <f>Sector_Fuels_ELC!L19</f>
         <v>FTE-ELCGAS</v>
@@ -5706,7 +5669,7 @@
       <c r="Q19" s="111"/>
       <c r="R19" s="111"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" ht="12.75">
       <c r="B20" s="25" t="str">
         <f>Sector_Fuels_ELC!L20</f>
         <v>FTE-ELCOIL</v>
@@ -5721,7 +5684,7 @@
       </c>
       <c r="E20" s="70">
         <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>4.9257354796510562E-2</v>
+        <v>0.049257354796510562</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="71">
@@ -5752,7 +5715,7 @@
       <c r="Q20" s="111"/>
       <c r="R20" s="111"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" ht="12.75">
       <c r="B21" s="25"/>
       <c r="C21" t="str">
         <f>'EB1'!I$2</f>
@@ -5761,7 +5724,7 @@
       <c r="D21" s="25"/>
       <c r="E21" s="70">
         <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>3.8926710484734312E-2</v>
+        <v>0.038926710484734312</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="71"/>
@@ -5788,7 +5751,7 @@
       <c r="Q21" s="117"/>
       <c r="R21" s="111"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" ht="12.75">
       <c r="B22" s="25"/>
       <c r="C22" t="str">
         <f>'EB1'!L$2</f>
@@ -5824,7 +5787,7 @@
       <c r="Q22" s="111"/>
       <c r="R22" s="111"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" ht="12.75">
       <c r="B23" s="25"/>
       <c r="C23" t="str">
         <f>'EB1'!M$2</f>
@@ -5833,7 +5796,7 @@
       <c r="D23" s="25"/>
       <c r="E23" s="70">
         <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>5.4758702573637796E-2</v>
+        <v>0.054758702573637796</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="71"/>
@@ -5860,7 +5823,7 @@
       <c r="Q23" s="113"/>
       <c r="R23" s="113"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" ht="12.75">
       <c r="B24" s="28" t="str">
         <f>Sector_Fuels_ELC!L21</f>
         <v>FTE-ELCNUC</v>
@@ -5903,7 +5866,7 @@
       <c r="Q24" s="113"/>
       <c r="R24" s="113"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" ht="12.75">
       <c r="B25" s="28" t="str">
         <f>Sector_Fuels_ELC!L22</f>
         <v>FTE-ELCBIO</v>
@@ -5946,7 +5909,7 @@
       <c r="Q25" s="113"/>
       <c r="R25" s="113"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" ht="12.75">
       <c r="B26" s="28" t="str">
         <f>Sector_Fuels_ELC!L23</f>
         <v>FTE-ELCHYD</v>
@@ -5968,7 +5931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" ht="12.75">
       <c r="B27" s="28" t="str">
         <f>Sector_Fuels_ELC!L24</f>
         <v>FTE-ELCWIN</v>
@@ -5990,7 +5953,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" ht="12.75">
       <c r="B28" s="28" t="str">
         <f>Sector_Fuels_ELC!L25</f>
         <v>FTE-ELCSOL</v>
@@ -6012,13 +5975,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" ht="12.75">
       <c r="B32" s="52"/>
       <c r="C32" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3" ht="12.75">
       <c r="B33" s="68"/>
       <c r="C33" s="1" t="s">
         <v>145</v>
@@ -6026,46 +5989,46 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:AB65536"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85428571428571" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="25" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.4285714285714" style="25" customWidth="1"/>
+    <col min="3" max="3" width="12.1428571428571" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.2857142857143" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.14285714285714" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.2857142857143" style="25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.14285714285714" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="43.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.28571428571429" customWidth="1"/>
+    <col min="25" max="25" width="11.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5714285714286" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.85546875" style="25"/>
+    <col min="28" max="28" width="8.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.85714285714286" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="30">
       <c r="B1" s="24" t="s">
         <v>65</v>
       </c>
@@ -6088,7 +6051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:28" ht="31.5">
       <c r="B2" s="14" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -6126,7 +6089,7 @@
       <c r="AA2" s="107"/>
       <c r="AB2" s="107"/>
     </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="20:28" ht="12.75">
       <c r="T3" s="108" t="s">
         <v>7</v>
       </c>
@@ -6155,7 +6118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" s="26" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:28" s="26" customFormat="1" ht="30.75" thickBot="1">
       <c r="B4" s="33" t="s">
         <v>107</v>
       </c>
@@ -6202,7 +6165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" s="26" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:28" s="26" customFormat="1" ht="15.75">
       <c r="B5" s="32" t="s">
         <v>113</v>
       </c>
@@ -6246,7 +6209,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="20:28" ht="12.75">
       <c r="T6" s="113" t="s">
         <v>88</v>
       </c>
@@ -6268,11 +6231,11 @@
       <c r="AA6" s="113"/>
       <c r="AB6" s="113"/>
     </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="20:21" ht="12.75">
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="4:28" ht="12.75">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -6297,7 +6260,7 @@
       <c r="AA8" s="107"/>
       <c r="AB8" s="107"/>
     </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:28" ht="12.75" customHeight="1">
       <c r="B9" s="21" t="s">
         <v>1</v>
       </c>
@@ -6376,7 +6339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28" ht="23.25" thickBot="1">
       <c r="B10" s="19" t="s">
         <v>37</v>
       </c>
@@ -6455,7 +6418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:28" ht="13.5" thickBot="1">
       <c r="B11" s="18" t="s">
         <v>76</v>
       </c>
@@ -6516,9 +6479,9 @@
       <c r="AA11" s="110"/>
       <c r="AB11" s="110"/>
     </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:28" ht="12.75">
       <c r="B12" s="25" t="str">
-        <f t="shared" ref="B12:B19" si="0">V12</f>
+        <f t="shared" si="0" ref="B12:B19">V12</f>
         <v>ELCTECOA00</v>
       </c>
       <c r="C12" s="25" t="str">
@@ -6526,7 +6489,7 @@
         <v>ELCCOA</v>
       </c>
       <c r="D12" s="25" t="str">
-        <f t="shared" ref="D12:D19" si="1">$V$5</f>
+        <f t="shared" si="1" ref="D12:D19">$V$5</f>
         <v>ELC</v>
       </c>
       <c r="G12" s="98">
@@ -6545,7 +6508,7 @@
         <v>40</v>
       </c>
       <c r="M12" s="76">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="N12" s="75">
         <v>30</v>
@@ -6558,7 +6521,7 @@
       </c>
       <c r="Q12" s="26"/>
       <c r="R12" s="34">
-        <f t="shared" ref="R12:R19" si="2">G12*$J12*$O12</f>
+        <f t="shared" si="2" ref="R12:R19">G12*$J12*$O12</f>
         <v>2395.6907520000004</v>
       </c>
       <c r="S12" s="100"/>
@@ -6575,11 +6538,11 @@
         <v>Power Plants Existing00 - Solid Fuels</v>
       </c>
       <c r="X12" s="111" t="str">
-        <f t="shared" ref="X12:X19" si="3">$E$2</f>
+        <f t="shared" si="3" ref="X12:X19">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y12" s="111" t="str">
-        <f t="shared" ref="Y12:Y19" si="4">$F$2</f>
+        <f t="shared" si="4" ref="Y12:Y19">$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z12" s="115" t="s">
@@ -6588,7 +6551,7 @@
       <c r="AA12" s="111"/>
       <c r="AB12" s="111"/>
     </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:28" ht="12.75">
       <c r="B13" s="25" t="str">
         <f t="shared" si="0"/>
         <v>ELCTEGAS00</v>
@@ -6617,7 +6580,7 @@
         <v>35</v>
       </c>
       <c r="M13" s="76">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="N13" s="75">
         <v>20</v>
@@ -6656,7 +6619,7 @@
       <c r="AA13" s="111"/>
       <c r="AB13" s="111"/>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:28" ht="12.75">
       <c r="B14" s="25" t="str">
         <f t="shared" si="0"/>
         <v>ELCTEOIL00</v>
@@ -6685,7 +6648,7 @@
         <v>20</v>
       </c>
       <c r="M14" s="94">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="N14" s="93">
         <v>30</v>
@@ -6724,7 +6687,7 @@
       <c r="AA14" s="111"/>
       <c r="AB14" s="111"/>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:28" ht="12.75">
       <c r="B15" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ELCNENUC00</v>
@@ -6751,7 +6714,7 @@
         <v>0.33</v>
       </c>
       <c r="J15" s="94">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="K15" s="93"/>
       <c r="L15" s="94">
@@ -6797,7 +6760,7 @@
       <c r="AA15" s="111"/>
       <c r="AB15" s="111"/>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:28" ht="12.75">
       <c r="B16" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ELCREBIO00</v>
@@ -6821,7 +6784,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="73">
-        <v>0.6</v>
+        <v>0.60</v>
       </c>
       <c r="K16" s="73"/>
       <c r="L16" s="74">
@@ -6867,7 +6830,7 @@
       <c r="AA16" s="111"/>
       <c r="AB16" s="111"/>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:28" ht="12.75">
       <c r="B17" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ELCREHYD00</v>
@@ -6892,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="73">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="K17" s="73"/>
       <c r="L17" s="74">
@@ -6908,7 +6871,7 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P17" s="94">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="Q17" s="28"/>
       <c r="R17" s="34">
@@ -6938,7 +6901,7 @@
       <c r="AA17" s="111"/>
       <c r="AB17" s="111"/>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:28" ht="12.75">
       <c r="B18" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ELCREWIN00</v>
@@ -6969,7 +6932,7 @@
         <v>35</v>
       </c>
       <c r="M18" s="73">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="N18" s="74">
         <v>20</v>
@@ -6978,7 +6941,7 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P18" s="94">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="34">
@@ -7008,7 +6971,7 @@
       <c r="AA18" s="111"/>
       <c r="AB18" s="111"/>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:28" ht="12.75">
       <c r="B19" s="28" t="str">
         <f t="shared" si="0"/>
         <v>ELCRESOL00</v>
@@ -7032,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="73">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="K19" s="73"/>
       <c r="L19" s="74">
@@ -7046,7 +7009,7 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P19" s="94">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="Q19" s="28"/>
       <c r="R19" s="34">
@@ -7076,49 +7039,49 @@
       <c r="AA19" s="111"/>
       <c r="AB19" s="111"/>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="18:18" ht="12.75">
       <c r="R21" s="97"/>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="18:18" ht="12.75">
       <c r="R22" s="97"/>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" ht="12.75">
       <c r="B23" s="52"/>
       <c r="C23" s="1" t="s">
         <v>144</v>
       </c>
       <c r="R23" s="97"/>
     </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" ht="12.75">
       <c r="B24" s="68"/>
       <c r="C24" s="1" t="s">
         <v>145</v>
       </c>
       <c r="R24" s="97"/>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="18:18" ht="12.75">
       <c r="R25" s="97"/>
     </row>
-    <row r="65536" spans="19:19" x14ac:dyDescent="0.2">
+    <row r="65536" spans="19:19" ht="12.75">
       <c r="S65536" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="17.45" customHeight="1">
       <c r="B3" s="42" t="s">
         <v>150</v>
       </c>
@@ -7131,7 +7094,7 @@
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
     </row>
-    <row r="4" spans="2:10" s="6" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" s="6" customFormat="1" ht="17.45" customHeight="1">
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
@@ -7139,7 +7102,7 @@
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
     </row>
-    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="18">
       <c r="B5" s="40" t="s">
         <v>138</v>
       </c>
@@ -7147,7 +7110,7 @@
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="13.5" thickBot="1">
       <c r="B6" s="45" t="s">
         <v>0</v>
       </c>
@@ -7167,7 +7130,7 @@
       <c r="G6" s="44"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="13.5" thickBot="1">
       <c r="B7" s="18" t="s">
         <v>76</v>
       </c>
@@ -7184,7 +7147,7 @@
       <c r="G7" s="88"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" ht="12.75">
       <c r="B8" s="25" t="str">
         <f>Con_ELC!$V$6</f>
         <v>ELCCO2</v>
@@ -7193,7 +7156,7 @@
         <v>95</v>
       </c>
       <c r="D8" s="73">
-        <v>56.1</v>
+        <v>56.10</v>
       </c>
       <c r="E8" s="73">
         <v>76.400000000000006</v>
@@ -7202,21 +7165,21 @@
       <c r="G8" s="89"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:7" ht="12.75">
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:7" ht="12.75">
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" ht="12.75">
       <c r="B23" s="52"/>
       <c r="C23" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="68"/>
       <c r="C24" s="1" t="s">
         <v>145</v>

--- a/VT_REG1_ELC_V12.xlsx
+++ b/VT_REG1_ELC_V12.xlsx
@@ -1,43 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-test_model\Demo_S012_Vonline\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816C9C6B-95DD-4519-9B4A-93A77CDB566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" tabRatio="901" activeTab="3"/>
+    <workbookView xWindow="6540" yWindow="2505" windowWidth="21600" windowHeight="11295" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EB1" sheetId="133" r:id="rId3"/>
-    <sheet name="RES_ELC" sheetId="152" r:id="rId4"/>
-    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId5"/>
-    <sheet name="Con_ELC" sheetId="143" r:id="rId6"/>
-    <sheet name="Emi" sheetId="149" r:id="rId7"/>
+    <sheet name="EB1" sheetId="133" r:id="rId1"/>
+    <sheet name="RES_ELC" sheetId="152" r:id="rId2"/>
+    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId3"/>
+    <sheet name="Con_ELC" sheetId="143" r:id="rId4"/>
+    <sheet name="Emi" sheetId="149" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
@@ -45,7 +51,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -172,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2">
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -238,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -286,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -316,7 +322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="2">
+    <comment ref="P15" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -400,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="1">
+    <comment ref="Q15" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -423,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="2">
+    <comment ref="R15" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -480,7 +486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="2">
+    <comment ref="J16" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -703,7 +709,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
@@ -711,7 +717,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -814,7 +820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="1">
+    <comment ref="Y3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -838,7 +844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="2">
+    <comment ref="Z3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="2">
+    <comment ref="AA3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -952,7 +958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="2">
+    <comment ref="AB3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -982,7 +988,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="2">
+    <comment ref="Z9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1066,7 +1072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="1">
+    <comment ref="AA9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1089,7 +1095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="2">
+    <comment ref="AB9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1146,7 +1152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T10" authorId="2">
+    <comment ref="T10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1879,16 +1885,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="186" formatCode="0.000"/>
-    <numFmt numFmtId="187" formatCode="General_)"/>
-    <numFmt numFmtId="188" formatCode="0.0"/>
-    <numFmt numFmtId="190" formatCode="0.0000"/>
-    <numFmt numFmtId="195" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="General_)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2040,7 +2046,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="9" tint="-0.249970003962517"/>
+      <color theme="9" tint="-0.24994659260841701"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2058,6 +2064,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -2068,13 +2079,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799979984760284"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990010261536"/>
+        <fgColor theme="6" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2110,7 +2121,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799979984760284"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2122,7 +2133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990010261536"/>
+        <fgColor theme="5" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2134,31 +2145,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799979984760284"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799979984760284"/>
+        <fgColor theme="6" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799979984760284"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799979984760284"/>
+        <fgColor theme="3" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990010261536"/>
+        <fgColor theme="9" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2184,6 +2195,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2192,6 +2204,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2202,6 +2215,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2210,6 +2224,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2220,6 +2235,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2228,6 +2244,7 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2242,6 +2259,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2256,6 +2274,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2270,6 +2289,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2282,6 +2302,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2294,6 +2315,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2304,6 +2326,7 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2316,6 +2339,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2328,6 +2352,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2340,6 +2365,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2348,6 +2374,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2358,6 +2385,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2368,6 +2396,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2376,205 +2405,131 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="48">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="101">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="122">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyBorder="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="10"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="11" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="22" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2584,32 +2539,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="15" fillId="7" borderId="0" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="7" borderId="6" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="187" fontId="13" fillId="5" borderId="7" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="0" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="6" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="7" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="5" borderId="8" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="8" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="5" borderId="9" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="9" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="5" borderId="10" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2618,7 +2567,7 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2630,237 +2579,116 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="10" applyFill="1"/>
+    <xf numFmtId="2" fontId="26" fillId="14" borderId="0" xfId="10" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
     </xf>
-    <xf numFmtId="187" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="8" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1" applyBorder="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="26" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="3" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="195" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="34">
+  <cellStyles count="30">
+    <cellStyle name="20% - Accent5" xfId="2" builtinId="46"/>
+    <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
+    <cellStyle name="Accent2" xfId="4" builtinId="33"/>
+    <cellStyle name="Calculation" xfId="5" builtinId="22"/>
+    <cellStyle name="Comma 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Good" xfId="7" builtinId="26"/>
+    <cellStyle name="Input" xfId="8" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="9" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
-    <cellStyle name="20% - Accent5" xfId="20" builtinId="46"/>
-    <cellStyle name="40% - Accent3" xfId="21" builtinId="39"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
-    <cellStyle name="Calculation" xfId="23" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="24"/>
-    <cellStyle name="Good" xfId="25" builtinId="26"/>
-    <cellStyle name="Input" xfId="26" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="27" builtinId="28"/>
-    <cellStyle name="Normal 10" xfId="28"/>
-    <cellStyle name="Normal 2" xfId="29"/>
-    <cellStyle name="Normal 4" xfId="30"/>
-    <cellStyle name="Normal 4 2" xfId="31"/>
-    <cellStyle name="Normal 8" xfId="32"/>
-    <cellStyle name="Normal 9 2" xfId="33"/>
-    <cellStyle name="Normale_B2020" xfId="34"/>
-    <cellStyle name="Percent 2" xfId="35"/>
-    <cellStyle name="Percent 3" xfId="36"/>
-    <cellStyle name="Percent 3 2" xfId="37"/>
-    <cellStyle name="Percent 3 3" xfId="38"/>
-    <cellStyle name="Percent 3 4" xfId="39"/>
-    <cellStyle name="Percent 4" xfId="40"/>
-    <cellStyle name="Percent 4 2" xfId="41"/>
-    <cellStyle name="Percent 4 3" xfId="42"/>
-    <cellStyle name="Percent 4 4" xfId="43"/>
-    <cellStyle name="Percent 5" xfId="44"/>
-    <cellStyle name="Percent 6" xfId="45"/>
-    <cellStyle name="Percent 7" xfId="46"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="47"/>
+    <cellStyle name="Normal 10" xfId="10" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 4" xfId="12" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 8" xfId="14" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 9 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normale_B2020" xfId="16" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Percent 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Percent 3 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Percent 3 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Percent 3 4" xfId="21" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Percent 4" xfId="22" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Percent 4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Percent 4 3" xfId="24" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Percent 4 4" xfId="25" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Percent 5" xfId="26" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Percent 6" xfId="27" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Percent 7" xfId="28" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="29" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2873,7 +2701,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2892,7 +2720,7 @@
         <xdr:cNvPr id="56975" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07b54768-2264-459d-aaaf-4e7cad4688c6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07B54768-2264-459D-AAAF-4E7CAD4688C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2901,7 +2729,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -2917,7 +2745,9 @@
           <a:off x="123825" y="962025"/>
           <a:ext cx="800100" cy="2238375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -2963,7 +2793,7 @@
         <xdr:cNvPr id="56976" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998f4-daf5-4ab5-a34b-dfa9cc7ff7f7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998F4-DAF5-4AB5-A34B-DFA9CC7FF7F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2972,7 +2802,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -2988,7 +2818,9 @@
           <a:off x="1552575" y="18926175"/>
           <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3034,7 +2866,7 @@
         <xdr:cNvPr id="56977" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ad288841-d70d-4c2e-9a6a-06c46b032c2b}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD288841-D70D-4C2E-9A6A-06C46B032C2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3043,7 +2875,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -3059,7 +2891,9 @@
           <a:off x="1552575" y="1104900"/>
           <a:ext cx="6524625" cy="3905250"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3105,7 +2939,7 @@
         <xdr:cNvPr id="56978" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f7edbe9c-2ffc-4928-ae9b-df9bbbde5c06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7EDBE9C-2FFC-4928-AE9B-DF9BBBDE5C06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3114,7 +2948,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
@@ -3130,7 +2964,9 @@
           <a:off x="1552575" y="4962525"/>
           <a:ext cx="3343275" cy="952500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3162,7 +2998,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3176,12 +3012,12 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f6b2f145-8850-4388-9ade-b2c38cec5f7b}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6B2F145-8850-4388-9ADE-B2C38CEC5F7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3192,7 +3028,9 @@
           <a:off x="6534150" y="4933950"/>
           <a:ext cx="6372225" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3319,7 +3157,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
@@ -3333,12 +3171,12 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>1090</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32d1cae3-ab1f-44e7-83a8-8cfe9f3a6676}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D1CAE3-AB1F-44E7-83A8-8CFE9F3A6676}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3349,7 +3187,9 @@
           <a:off x="12925425" y="4276725"/>
           <a:ext cx="6477000" cy="1285875"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3455,7 +3295,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3469,12 +3309,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bd1a3727-b21e-4010-995e-8645c474e6c5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1A3727-B21E-4010-995E-8645C474E6C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3485,7 +3325,9 @@
           <a:off x="609600" y="2143125"/>
           <a:ext cx="4391025" cy="552450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3561,7 +3403,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -3696,8 +3538,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EnergyBalance"/>
       <sheetName val="EB1"/>
@@ -3709,28 +3554,28 @@
       <sheetData sheetId="1">
         <row r="10">
           <cell r="D10">
-            <v>-37.4647</v>
+            <v>-37.464700000000001</v>
           </cell>
           <cell r="E10">
-            <v>-317.192</v>
+            <v>-317.19200000000001</v>
           </cell>
           <cell r="F10">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>-16.284</v>
+            <v>-16.283999999999999</v>
           </cell>
           <cell r="H10">
-            <v>-0.0215</v>
+            <v>-2.1499999999999998E-2</v>
           </cell>
           <cell r="I10">
-            <v>-528.761</v>
+            <v>-528.76099999999997</v>
           </cell>
           <cell r="J10">
-            <v>-164.508</v>
+            <v>-164.50800000000001</v>
           </cell>
           <cell r="K10">
-            <v>-0.616</v>
+            <v>-0.61599999999999999</v>
           </cell>
           <cell r="L10">
             <v>-205.88</v>
@@ -3763,27 +3608,27 @@
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>-1274.69945</v>
+            <v>-1274.6994499999998</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>-6238.778</v>
+            <v>-6238.7780000000012</v>
           </cell>
           <cell r="E11">
-            <v>-2254.2176</v>
+            <v>-2254.2175999999999</v>
           </cell>
           <cell r="F11">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>-30.1605</v>
+            <v>-30.160499999999999</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>-23.835</v>
+            <v>-23.835000000000001</v>
           </cell>
           <cell r="J11">
             <v>0</v>
@@ -3795,16 +3640,16 @@
             <v>-524.78</v>
           </cell>
           <cell r="M11">
-            <v>-33.529</v>
+            <v>-33.529000000000003</v>
           </cell>
           <cell r="N11">
             <v>-4455</v>
           </cell>
           <cell r="O11">
-            <v>-527.2591875</v>
+            <v>-527.25918750000005</v>
           </cell>
           <cell r="P11">
-            <v>-502.66</v>
+            <v>-502.66000000000008</v>
           </cell>
           <cell r="Q11">
             <v>-263.8965</v>
@@ -3813,16 +3658,16 @@
             <v>-68</v>
           </cell>
           <cell r="S11">
-            <v>-16.4745</v>
+            <v>-16.474499999999999</v>
           </cell>
           <cell r="T11">
-            <v>868.7795</v>
+            <v>868.77949999999998</v>
           </cell>
           <cell r="U11">
             <v>5790.5</v>
           </cell>
           <cell r="V11">
-            <v>-8279.3107875</v>
+            <v>-8279.3107875000023</v>
           </cell>
         </row>
         <row r="12">
@@ -3836,13 +3681,13 @@
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>-7.619</v>
+            <v>-7.6189999999999998</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>-0.2335</v>
+            <v>-0.23350000000000001</v>
           </cell>
           <cell r="J12">
             <v>0</v>
@@ -3872,16 +3717,16 @@
             <v>0</v>
           </cell>
           <cell r="S12">
-            <v>-0.7845</v>
+            <v>-0.78449999999999998</v>
           </cell>
           <cell r="T12">
-            <v>329.3715</v>
+            <v>329.37150000000003</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>-26.8205499999999</v>
+            <v>-26.820549999999912</v>
           </cell>
         </row>
         <row r="13">
@@ -3898,22 +3743,22 @@
             <v>5701.34</v>
           </cell>
           <cell r="H13">
-            <v>969.478</v>
+            <v>969.47799999999995</v>
           </cell>
           <cell r="I13">
-            <v>1086.304</v>
+            <v>1086.3040000000001</v>
           </cell>
           <cell r="J13">
-            <v>3354.912</v>
+            <v>3354.9119999999998</v>
           </cell>
           <cell r="K13">
-            <v>970.288</v>
+            <v>970.28800000000001</v>
           </cell>
           <cell r="L13">
-            <v>2285.102</v>
+            <v>2285.1019999999999</v>
           </cell>
           <cell r="M13">
-            <v>1299.945</v>
+            <v>1299.9449999999999</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -3940,7 +3785,7 @@
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>-200.8615</v>
+            <v>-200.86150000000021</v>
           </cell>
         </row>
       </sheetData>
@@ -4298,1291 +4143,1241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="5" tint="-0.249970003962517"/>
+    <tabColor theme="5" tint="-0.24994659260841701"/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <dimension ref="B1:AA17"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="12.1428571428571" customWidth="1"/>
-    <col min="9" max="12" width="10.8571428571429" customWidth="1"/>
-    <col min="13" max="13" width="17.8571428571429" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.8571428571429" customWidth="1"/>
-    <col min="22" max="22" width="7.28571428571429" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.71428571428571" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28571428571429" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="24:27" s="6" customFormat="1" ht="12.75">
-      <c r="X1" s="23" t="s">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="X1" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>80</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="3:27" ht="15.75">
-      <c r="C2" s="7"/>
-      <c r="D2" s="48" t="s">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="48" t="s">
+      <c r="K2" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="L2" s="48" t="s">
+      <c r="L2" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="M2" s="48" t="s">
+      <c r="M2" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="48" t="s">
+      <c r="O2" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="Q2" s="48" t="s">
+      <c r="Q2" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="R2" s="48" t="s">
+      <c r="R2" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="S2" s="48" t="s">
+      <c r="S2" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="T2" s="48" t="s">
+      <c r="T2" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="U2" s="48" t="s">
+      <c r="U2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="48" t="s">
+      <c r="V2" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="47" t="s">
+      <c r="Y2" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AA2" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="3:22" ht="25.5">
-      <c r="C3" s="67" t="s">
+    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C3" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="F3" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="49" t="s">
+      <c r="J3" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="K3" s="49" t="s">
+      <c r="K3" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="49" t="s">
+      <c r="L3" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="49" t="s">
+      <c r="M3" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="N3" s="49" t="s">
+      <c r="N3" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="49" t="s">
+      <c r="O3" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="P3" s="49" t="s">
+      <c r="P3" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="Q3" s="49" t="s">
+      <c r="Q3" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="R3" s="49" t="s">
+      <c r="R3" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="S3" s="49" t="s">
+      <c r="S3" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="49" t="s">
+      <c r="T3" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="49" t="s">
+      <c r="U3" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="V3" s="49" t="s">
+      <c r="V3" s="42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="12.75">
-      <c r="B4" s="46"/>
-      <c r="C4" s="83" t="s">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B4" s="39"/>
+      <c r="C4" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="84"/>
-      <c r="X4" s="6"/>
-    </row>
-    <row r="5" spans="2:24" ht="12.75">
-      <c r="B5" s="50" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="76"/>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B5" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="51">
-        <f>'[2]EB1'!D10</f>
+      <c r="D5" s="44">
+        <f>[2]EB1!D10</f>
         <v>-37.464700000000001</v>
       </c>
-      <c r="E5" s="51">
-        <f>'[2]EB1'!E10</f>
+      <c r="E5" s="44">
+        <f>[2]EB1!E10</f>
         <v>-317.19200000000001</v>
       </c>
-      <c r="F5" s="51">
-        <f>'[2]EB1'!F10</f>
+      <c r="F5" s="44">
+        <f>[2]EB1!F10</f>
         <v>0</v>
       </c>
-      <c r="G5" s="51">
-        <f>'[2]EB1'!G10</f>
+      <c r="G5" s="44">
+        <f>[2]EB1!G10</f>
         <v>-16.283999999999999</v>
       </c>
-      <c r="H5" s="51">
-        <f>'[2]EB1'!H10</f>
-        <v>-0.021499999999999998</v>
-      </c>
-      <c r="I5" s="51">
-        <f>'[2]EB1'!I10</f>
+      <c r="H5" s="44">
+        <f>[2]EB1!H10</f>
+        <v>-2.1499999999999998E-2</v>
+      </c>
+      <c r="I5" s="44">
+        <f>[2]EB1!I10</f>
         <v>-528.76099999999997</v>
       </c>
-      <c r="J5" s="51">
-        <f>'[2]EB1'!J10</f>
+      <c r="J5" s="44">
+        <f>[2]EB1!J10</f>
         <v>-164.50800000000001</v>
       </c>
-      <c r="K5" s="51">
-        <f>'[2]EB1'!K10</f>
+      <c r="K5" s="44">
+        <f>[2]EB1!K10</f>
         <v>-0.61599999999999999</v>
       </c>
-      <c r="L5" s="51">
-        <f>'[2]EB1'!L10</f>
+      <c r="L5" s="44">
+        <f>[2]EB1!L10</f>
         <v>-205.88</v>
       </c>
-      <c r="M5" s="51">
-        <f>'[2]EB1'!M10</f>
+      <c r="M5" s="44">
+        <f>[2]EB1!M10</f>
         <v>0</v>
       </c>
-      <c r="N5" s="51">
-        <f>'[2]EB1'!N10</f>
+      <c r="N5" s="44">
+        <f>[2]EB1!N10</f>
         <v>0</v>
       </c>
-      <c r="O5" s="51">
-        <f>'[2]EB1'!O10</f>
+      <c r="O5" s="44">
+        <f>[2]EB1!O10</f>
         <v>-3.21225</v>
       </c>
-      <c r="P5" s="51">
-        <f>'[2]EB1'!P10</f>
+      <c r="P5" s="44">
+        <f>[2]EB1!P10</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="51">
-        <f>'[2]EB1'!Q10</f>
+      <c r="Q5" s="44">
+        <f>[2]EB1!Q10</f>
         <v>0</v>
       </c>
-      <c r="R5" s="51">
-        <f>'[2]EB1'!R10</f>
+      <c r="R5" s="44">
+        <f>[2]EB1!R10</f>
         <v>0</v>
       </c>
-      <c r="S5" s="51">
-        <f>'[2]EB1'!S10</f>
-        <v>-0.76000000000000001</v>
-      </c>
-      <c r="T5" s="51">
-        <f>'[2]EB1'!T10</f>
+      <c r="S5" s="44">
+        <f>[2]EB1!S10</f>
+        <v>-0.76</v>
+      </c>
+      <c r="T5" s="44">
+        <f>[2]EB1!T10</f>
         <v>0</v>
       </c>
-      <c r="U5" s="51">
-        <f>'[2]EB1'!U10</f>
+      <c r="U5" s="44">
+        <f>[2]EB1!U10</f>
         <v>0</v>
       </c>
-      <c r="V5" s="85">
-        <f>'[2]EB1'!V10</f>
+      <c r="V5" s="77">
+        <f>[2]EB1!V10</f>
         <v>-1274.6994499999998</v>
       </c>
-      <c r="X5" s="6"/>
-    </row>
-    <row r="6" spans="2:24" ht="15">
-      <c r="B6" s="50" t="s">
+    </row>
+    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B6" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="54">
-        <f>'[2]EB1'!D11</f>
+      <c r="D6" s="47">
+        <f>[2]EB1!D11</f>
         <v>-6238.7780000000012</v>
       </c>
-      <c r="E6" s="53">
-        <f>'[2]EB1'!E11</f>
+      <c r="E6" s="46">
+        <f>[2]EB1!E11</f>
         <v>-2254.2175999999999</v>
       </c>
-      <c r="F6" s="53">
-        <f>'[2]EB1'!F11</f>
+      <c r="F6" s="46">
+        <f>[2]EB1!F11</f>
         <v>0</v>
       </c>
-      <c r="G6" s="53">
-        <f>'[2]EB1'!G11</f>
+      <c r="G6" s="46">
+        <f>[2]EB1!G11</f>
         <v>-30.160499999999999</v>
       </c>
-      <c r="H6" s="53">
-        <f>'[2]EB1'!H11</f>
+      <c r="H6" s="46">
+        <f>[2]EB1!H11</f>
         <v>0</v>
       </c>
-      <c r="I6" s="53">
-        <f>'[2]EB1'!I11</f>
+      <c r="I6" s="46">
+        <f>[2]EB1!I11</f>
         <v>-23.835000000000001</v>
       </c>
-      <c r="J6" s="53">
-        <f>'[2]EB1'!J11</f>
+      <c r="J6" s="46">
+        <f>[2]EB1!J11</f>
         <v>0</v>
       </c>
-      <c r="K6" s="53">
-        <f>'[2]EB1'!K11</f>
+      <c r="K6" s="46">
+        <f>[2]EB1!K11</f>
         <v>0</v>
       </c>
-      <c r="L6" s="53">
-        <f>'[2]EB1'!L11</f>
-        <v>-524.77999999999997</v>
-      </c>
-      <c r="M6" s="53">
-        <f>'[2]EB1'!M11</f>
+      <c r="L6" s="46">
+        <f>[2]EB1!L11</f>
+        <v>-524.78</v>
+      </c>
+      <c r="M6" s="46">
+        <f>[2]EB1!M11</f>
         <v>-33.529000000000003</v>
       </c>
-      <c r="N6" s="53">
-        <f>'[2]EB1'!N11</f>
+      <c r="N6" s="46">
+        <f>[2]EB1!N11</f>
         <v>-4455</v>
       </c>
-      <c r="O6" s="53">
-        <f>'[2]EB1'!O11</f>
+      <c r="O6" s="46">
+        <f>[2]EB1!O11</f>
         <v>-527.25918750000005</v>
       </c>
-      <c r="P6" s="53">
-        <f>'[2]EB1'!P11</f>
+      <c r="P6" s="46">
+        <f>[2]EB1!P11</f>
         <v>-502.66000000000008</v>
       </c>
-      <c r="Q6" s="53">
-        <f>'[2]EB1'!Q11</f>
+      <c r="Q6" s="46">
+        <f>[2]EB1!Q11</f>
         <v>-263.8965</v>
       </c>
-      <c r="R6" s="53">
-        <f>'[2]EB1'!R11</f>
+      <c r="R6" s="46">
+        <f>[2]EB1!R11</f>
         <v>-68</v>
       </c>
-      <c r="S6" s="51">
-        <f>'[2]EB1'!S11</f>
+      <c r="S6" s="44">
+        <f>[2]EB1!S11</f>
         <v>-16.474499999999999</v>
       </c>
-      <c r="T6" s="51">
-        <f>'[2]EB1'!T11</f>
+      <c r="T6" s="44">
+        <f>[2]EB1!T11</f>
         <v>868.77949999999998</v>
       </c>
-      <c r="U6" s="53">
-        <f>'[2]EB1'!U11</f>
+      <c r="U6" s="46">
+        <f>[2]EB1!U11</f>
         <v>5790.5</v>
       </c>
-      <c r="V6" s="85">
-        <f>'[2]EB1'!V11</f>
+      <c r="V6" s="77">
+        <f>[2]EB1!V11</f>
         <v>-8279.3107875000023</v>
       </c>
-      <c r="X6" s="95"/>
-    </row>
-    <row r="7" spans="2:24" ht="12.75">
-      <c r="B7" s="50" t="s">
+      <c r="X6" s="84"/>
+    </row>
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B7" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="51">
-        <f>'[2]EB1'!D12</f>
+      <c r="D7" s="44">
+        <f>[2]EB1!D12</f>
         <v>-104.9074</v>
       </c>
-      <c r="E7" s="51">
-        <f>'[2]EB1'!E12</f>
+      <c r="E7" s="44">
+        <f>[2]EB1!E12</f>
         <v>-120.5204</v>
       </c>
-      <c r="F7" s="51">
-        <f>'[2]EB1'!F12</f>
+      <c r="F7" s="44">
+        <f>[2]EB1!F12</f>
         <v>0</v>
       </c>
-      <c r="G7" s="51">
-        <f>'[2]EB1'!G12</f>
+      <c r="G7" s="44">
+        <f>[2]EB1!G12</f>
         <v>-7.6189999999999998</v>
       </c>
-      <c r="H7" s="51">
-        <f>'[2]EB1'!H12</f>
+      <c r="H7" s="44">
+        <f>[2]EB1!H12</f>
         <v>0</v>
       </c>
-      <c r="I7" s="51">
-        <f>'[2]EB1'!I12</f>
+      <c r="I7" s="44">
+        <f>[2]EB1!I12</f>
         <v>-0.23350000000000001</v>
       </c>
-      <c r="J7" s="51">
-        <f>'[2]EB1'!J12</f>
+      <c r="J7" s="44">
+        <f>[2]EB1!J12</f>
         <v>0</v>
       </c>
-      <c r="K7" s="51">
-        <f>'[2]EB1'!K12</f>
+      <c r="K7" s="44">
+        <f>[2]EB1!K12</f>
         <v>0</v>
       </c>
-      <c r="L7" s="51">
-        <f>'[2]EB1'!L12</f>
-        <v>-15.199999999999999</v>
-      </c>
-      <c r="M7" s="51">
-        <f>'[2]EB1'!M12</f>
+      <c r="L7" s="44">
+        <f>[2]EB1!L12</f>
+        <v>-15.2</v>
+      </c>
+      <c r="M7" s="44">
+        <f>[2]EB1!M12</f>
         <v>-1.772</v>
       </c>
-      <c r="N7" s="51">
-        <f>'[2]EB1'!N12</f>
+      <c r="N7" s="44">
+        <f>[2]EB1!N12</f>
         <v>0</v>
       </c>
-      <c r="O7" s="51">
-        <f>'[2]EB1'!O12</f>
+      <c r="O7" s="44">
+        <f>[2]EB1!O12</f>
         <v>-105.15525</v>
       </c>
-      <c r="P7" s="51">
-        <f>'[2]EB1'!P12</f>
+      <c r="P7" s="44">
+        <f>[2]EB1!P12</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="51">
-        <f>'[2]EB1'!Q12</f>
+      <c r="Q7" s="44">
+        <f>[2]EB1!Q12</f>
         <v>0</v>
       </c>
-      <c r="R7" s="51">
-        <f>'[2]EB1'!R12</f>
+      <c r="R7" s="44">
+        <f>[2]EB1!R12</f>
         <v>0</v>
       </c>
-      <c r="S7" s="51">
-        <f>'[2]EB1'!S12</f>
+      <c r="S7" s="44">
+        <f>[2]EB1!S12</f>
         <v>-0.78449999999999998</v>
       </c>
-      <c r="T7" s="51">
-        <f>'[2]EB1'!T12</f>
+      <c r="T7" s="44">
+        <f>[2]EB1!T12</f>
         <v>329.37150000000003</v>
       </c>
-      <c r="U7" s="51">
-        <f>'[2]EB1'!U12</f>
+      <c r="U7" s="44">
+        <f>[2]EB1!U12</f>
         <v>0</v>
       </c>
-      <c r="V7" s="85">
-        <f>'[2]EB1'!V12</f>
+      <c r="V7" s="77">
+        <f>[2]EB1!V12</f>
         <v>-26.820549999999912</v>
       </c>
-      <c r="X7" s="6"/>
-    </row>
-    <row r="8" spans="2:22" ht="12.75">
-      <c r="B8" s="50" t="s">
+    </row>
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B8" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="74">
-        <f>'[2]EB1'!D13</f>
+      <c r="D8" s="44">
+        <f>[2]EB1!D13</f>
         <v>0</v>
       </c>
-      <c r="E8" s="51">
-        <f>'[2]EB1'!E13</f>
+      <c r="E8" s="44">
+        <f>[2]EB1!E13</f>
         <v>0</v>
       </c>
-      <c r="F8" s="51">
-        <f>'[2]EB1'!F13</f>
+      <c r="F8" s="44">
+        <f>[2]EB1!F13</f>
         <v>-15868.2305</v>
       </c>
-      <c r="G8" s="51">
-        <f>'[2]EB1'!G13</f>
-        <v>5701.3400000000001</v>
-      </c>
-      <c r="H8" s="51">
-        <f>'[2]EB1'!H13</f>
+      <c r="G8" s="44">
+        <f>[2]EB1!G13</f>
+        <v>5701.34</v>
+      </c>
+      <c r="H8" s="44">
+        <f>[2]EB1!H13</f>
         <v>969.47799999999995</v>
       </c>
-      <c r="I8" s="51">
-        <f>'[2]EB1'!I13</f>
+      <c r="I8" s="44">
+        <f>[2]EB1!I13</f>
         <v>1086.3040000000001</v>
       </c>
-      <c r="J8" s="51">
-        <f>'[2]EB1'!J13</f>
+      <c r="J8" s="44">
+        <f>[2]EB1!J13</f>
         <v>3354.9119999999998</v>
       </c>
-      <c r="K8" s="51">
-        <f>'[2]EB1'!K13</f>
+      <c r="K8" s="44">
+        <f>[2]EB1!K13</f>
         <v>970.28800000000001</v>
       </c>
-      <c r="L8" s="51">
-        <f>'[2]EB1'!L13</f>
+      <c r="L8" s="44">
+        <f>[2]EB1!L13</f>
         <v>2285.1019999999999</v>
       </c>
-      <c r="M8" s="51">
-        <f>'[2]EB1'!M13</f>
+      <c r="M8" s="44">
+        <f>[2]EB1!M13</f>
         <v>1299.9449999999999</v>
       </c>
-      <c r="N8" s="51">
-        <f>'[2]EB1'!N13</f>
+      <c r="N8" s="44">
+        <f>[2]EB1!N13</f>
         <v>0</v>
       </c>
-      <c r="O8" s="51">
-        <f>'[2]EB1'!O13</f>
+      <c r="O8" s="44">
+        <f>[2]EB1!O13</f>
         <v>0</v>
       </c>
-      <c r="P8" s="51">
-        <f>'[2]EB1'!P13</f>
+      <c r="P8" s="44">
+        <f>[2]EB1!P13</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="51">
-        <f>'[2]EB1'!Q13</f>
+      <c r="Q8" s="44">
+        <f>[2]EB1!Q13</f>
         <v>0</v>
       </c>
-      <c r="R8" s="51">
-        <f>'[2]EB1'!R13</f>
+      <c r="R8" s="44">
+        <f>[2]EB1!R13</f>
         <v>0</v>
       </c>
-      <c r="S8" s="51">
-        <f>'[2]EB1'!S13</f>
+      <c r="S8" s="44">
+        <f>[2]EB1!S13</f>
         <v>0</v>
       </c>
-      <c r="T8" s="51">
-        <f>'[2]EB1'!T13</f>
+      <c r="T8" s="44">
+        <f>[2]EB1!T13</f>
         <v>0</v>
       </c>
-      <c r="U8" s="51">
-        <f>'[2]EB1'!U13</f>
+      <c r="U8" s="44">
+        <f>[2]EB1!U13</f>
         <v>0</v>
       </c>
-      <c r="V8" s="85">
-        <f>'[2]EB1'!V13</f>
+      <c r="V8" s="77">
+        <f>[2]EB1!V13</f>
         <v>-200.86150000000021</v>
       </c>
     </row>
-    <row r="9" spans="2:22" ht="15">
-      <c r="B9" s="46"/>
-      <c r="C9" s="55" t="s">
+    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="39"/>
+      <c r="C9" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="51">
         <f>SUM(D5:D8)</f>
         <v>-6381.1501000000017</v>
       </c>
-      <c r="E9" s="56">
-        <f t="shared" si="0" ref="E9:U9">SUM(E5:E8)</f>
-        <v>-2691.9299999999998</v>
-      </c>
-      <c r="F9" s="56">
+      <c r="E9" s="49">
+        <f t="shared" ref="E9:U9" si="0">SUM(E5:E8)</f>
+        <v>-2691.93</v>
+      </c>
+      <c r="F9" s="49">
         <f t="shared" si="0"/>
         <v>-15868.2305</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="49">
         <f t="shared" si="0"/>
         <v>5647.2764999999999</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="49">
         <f t="shared" si="0"/>
         <v>969.45650000000001</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="49">
         <f t="shared" si="0"/>
         <v>533.47450000000003</v>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="49">
         <f t="shared" si="0"/>
         <v>3190.404</v>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="49">
         <f t="shared" si="0"/>
         <v>969.67200000000003</v>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="49">
         <f t="shared" si="0"/>
         <v>1539.2419999999997</v>
       </c>
-      <c r="M9" s="56">
+      <c r="M9" s="49">
         <f t="shared" si="0"/>
         <v>1264.644</v>
       </c>
-      <c r="N9" s="56">
+      <c r="N9" s="49">
         <f t="shared" si="0"/>
         <v>-4455</v>
       </c>
-      <c r="O9" s="56">
+      <c r="O9" s="49">
         <f t="shared" si="0"/>
         <v>-635.62668750000012</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="49">
         <f t="shared" si="0"/>
         <v>-502.66000000000008</v>
       </c>
-      <c r="Q9" s="56">
+      <c r="Q9" s="49">
         <f t="shared" si="0"/>
         <v>-263.8965</v>
       </c>
-      <c r="R9" s="56">
+      <c r="R9" s="49">
         <f t="shared" si="0"/>
         <v>-68</v>
       </c>
-      <c r="S9" s="56">
+      <c r="S9" s="49">
         <f t="shared" si="0"/>
         <v>-18.019000000000002</v>
       </c>
-      <c r="T9" s="56">
+      <c r="T9" s="49">
         <f t="shared" si="0"/>
         <v>1198.1510000000001</v>
       </c>
-      <c r="U9" s="56">
+      <c r="U9" s="49">
         <f t="shared" si="0"/>
         <v>5790.5</v>
       </c>
-      <c r="V9" s="57">
+      <c r="V9" s="50">
         <f>SUM(V5:V8)</f>
         <v>-9781.6922875000037</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="12.75">
-      <c r="A10" s="6"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:18" ht="12.75">
-      <c r="A11" s="6"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-    </row>
-    <row r="12" spans="1:13" ht="15">
-      <c r="A12" s="6"/>
-      <c r="C12" s="53" t="s">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+    </row>
+    <row r="12" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="C12" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:22" ht="12.75">
-      <c r="A13" s="6"/>
-      <c r="V13" s="8"/>
-    </row>
-    <row r="14" spans="1:22" ht="12.75">
-      <c r="A14" s="6"/>
-      <c r="V14" s="8"/>
-    </row>
-    <row r="15" spans="1:22" ht="12.75">
-      <c r="A15" s="6"/>
-      <c r="C15" s="64" t="s">
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="C15" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="V15" s="8"/>
-    </row>
-    <row r="16" spans="1:22" ht="12.75">
-      <c r="A16" s="6"/>
-      <c r="B16" s="23" t="s">
+    </row>
+    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B16" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="V16" s="8"/>
-    </row>
-    <row r="17" spans="2:5" ht="12.75">
-      <c r="B17" s="50" t="s">
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="90">
+      <c r="C17" s="82">
         <v>1</v>
       </c>
-      <c r="D17" s="63"/>
-      <c r="E17" s="91"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="83"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:M5"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:M5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.85714285714286" customWidth="1"/>
-    <col min="2" max="2" width="7.71428571428571" customWidth="1"/>
-    <col min="3" max="4" width="6.85714285714286" customWidth="1"/>
-    <col min="14" max="14" width="5.42857142857143" customWidth="1"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="6.85546875" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:6" ht="12.75">
-      <c r="E1" s="11"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="2:6" ht="18">
-      <c r="B2" s="78" t="s">
+    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="B2" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="4" spans="5:13" ht="18">
-      <c r="E4" s="119" t="s">
+    </row>
+    <row r="4" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="121"/>
-    </row>
-    <row r="5" spans="5:13" ht="12.75" customHeight="1">
-      <c r="E5" s="79" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.8571428571429" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28571428571429" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.14285714285714" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4285714285714" customWidth="1"/>
-    <col min="11" max="11" width="7.14285714285714" customWidth="1"/>
-    <col min="12" max="12" width="14.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
-    <col min="15" max="15" width="10.4285714285714" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.8571428571429" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.14285714285714" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15">
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="39"/>
-    </row>
-    <row r="2" spans="2:18" ht="31.5">
-      <c r="B2" s="14" t="str">
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
       </c>
-      <c r="C2" s="22" t="str">
+      <c r="C2" s="19" t="str">
         <f>'EB1'!C6</f>
         <v>Electricity Plants</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="12" t="str">
         <f>'EB1'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="12" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="J2" s="106" t="s">
+      <c r="H2" s="11"/>
+      <c r="J2" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="106"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="107"/>
-    </row>
-    <row r="3" spans="10:18" ht="12.75">
-      <c r="J3" s="108" t="s">
+      <c r="K2" s="93"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="J3" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="109" t="s">
+      <c r="K3" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="108" t="s">
+      <c r="L3" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="108" t="s">
+      <c r="M3" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="108" t="s">
+      <c r="N3" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="108" t="s">
+      <c r="O3" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="108" t="s">
+      <c r="P3" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="108" t="s">
+      <c r="Q3" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="108" t="s">
+      <c r="R3" s="95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="J4" s="110" t="s">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="J4" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="110" t="s">
+      <c r="K4" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="110" t="s">
+      <c r="L4" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="110" t="s">
+      <c r="M4" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="110" t="s">
+      <c r="N4" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="110" t="s">
+      <c r="O4" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="110" t="s">
+      <c r="P4" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="110" t="s">
+      <c r="Q4" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="110" t="s">
+      <c r="R4" s="97" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="12.75">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="15"/>
-      <c r="J5" s="111" t="s">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="13"/>
+      <c r="J5" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111" t="str">
+      <c r="K5" s="94"/>
+      <c r="L5" s="94" t="str">
         <f>$B$2&amp;'EB1'!$D$2</f>
         <v>ELCCOA</v>
       </c>
-      <c r="M5" s="112" t="str">
+      <c r="M5" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$D$3</f>
         <v>Electricity Plants Solid Fuels</v>
       </c>
-      <c r="N5" s="111" t="str">
-        <f t="shared" si="0" ref="N5:N12">$E$2</f>
+      <c r="N5" s="94" t="str">
+        <f t="shared" ref="N5:N12" si="0">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-    </row>
-    <row r="6" spans="2:18" ht="12.75">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="15"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111" t="str">
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="13"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94" t="str">
         <f>$B$2&amp;'EB1'!$E$2</f>
         <v>ELCGAS</v>
       </c>
-      <c r="M6" s="112" t="str">
+      <c r="M6" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$E$3</f>
         <v>Electricity Plants Natural Gas</v>
       </c>
-      <c r="N6" s="111" t="str">
+      <c r="N6" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O6" s="111"/>
-      <c r="P6" s="111"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="111"/>
-    </row>
-    <row r="7" spans="2:18" ht="12.75">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="15"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111" t="str">
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="13"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94" t="str">
         <f>$B$2&amp;'EB1'!$F$2</f>
         <v>ELCOIL</v>
       </c>
-      <c r="M7" s="112" t="str">
+      <c r="M7" s="98" t="str">
         <f>$C$2&amp;" "&amp;RIGHT('EB1'!$F$3,3)</f>
         <v>Electricity Plants oil</v>
       </c>
-      <c r="N7" s="111" t="str">
+      <c r="N7" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
-      <c r="R7" s="111"/>
-    </row>
-    <row r="8" spans="2:18" ht="12.75">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="15"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111" t="str">
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="13"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94" t="str">
         <f>$B$2&amp;'EB1'!$N$2</f>
         <v>ELCNUC</v>
       </c>
-      <c r="M8" s="112" t="str">
+      <c r="M8" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$N$3</f>
         <v>Electricity Plants Nuclear Energy</v>
       </c>
-      <c r="N8" s="111" t="str">
+      <c r="N8" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O8" s="111"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="111"/>
-    </row>
-    <row r="9" spans="2:18" ht="12.75">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="15"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111" t="str">
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="94"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="13"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94" t="str">
         <f>$B$2&amp;'EB1'!$O$2</f>
         <v>ELCBIO</v>
       </c>
-      <c r="M9" s="112" t="str">
+      <c r="M9" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$O$3</f>
         <v>Electricity Plants Biomass</v>
       </c>
-      <c r="N9" s="111" t="str">
+      <c r="N9" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
-    </row>
-    <row r="10" spans="2:18" ht="12.75">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="15"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111" t="str">
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="13"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94" t="str">
         <f>$B$2&amp;'EB1'!$P$2</f>
         <v>ELCHYD</v>
       </c>
-      <c r="M10" s="112" t="str">
+      <c r="M10" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$P$3</f>
         <v>Electricity Plants Hydro power</v>
       </c>
-      <c r="N10" s="111" t="str">
+      <c r="N10" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O10" s="111"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="111"/>
-    </row>
-    <row r="11" spans="2:18" ht="12.75">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="15"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111" t="str">
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="13"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="94" t="str">
         <f>$B$2&amp;'EB1'!$Q$2</f>
         <v>ELCWIN</v>
       </c>
-      <c r="M11" s="112" t="str">
+      <c r="M11" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$Q$3</f>
         <v>Electricity Plants Wind energy</v>
       </c>
-      <c r="N11" s="111" t="str">
+      <c r="N11" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O11" s="111"/>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="111"/>
-    </row>
-    <row r="12" spans="2:18" ht="12.75">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="15"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111" t="str">
+      <c r="O11" s="94"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="13"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94" t="str">
         <f>$B$2&amp;'EB1'!$R$2</f>
         <v>ELCSOL</v>
       </c>
-      <c r="M12" s="112" t="str">
+      <c r="M12" s="98" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$R$3</f>
         <v>Electricity Plants Solar energy</v>
       </c>
-      <c r="N12" s="111" t="str">
+      <c r="N12" s="94" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="111"/>
-    </row>
-    <row r="13" spans="12:13" ht="12.75">
-      <c r="L13" s="27"/>
-      <c r="M13" s="29"/>
-    </row>
-    <row r="14" spans="4:18" ht="12.75">
-      <c r="D14" s="4" t="s">
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="J14" s="106" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="J14" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="K14" s="106"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
-      <c r="O14" s="113"/>
-      <c r="P14" s="113"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="113"/>
-    </row>
-    <row r="15" spans="2:18" ht="12.75">
-      <c r="B15" s="20" t="s">
+      <c r="K14" s="93"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="80" t="s">
+      <c r="F15" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="80" t="s">
+      <c r="H15" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="108" t="s">
+      <c r="J15" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="109" t="s">
+      <c r="K15" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="108" t="s">
+      <c r="L15" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="108" t="s">
+      <c r="M15" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="N15" s="108" t="s">
+      <c r="N15" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="108" t="s">
+      <c r="O15" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="108" t="s">
+      <c r="P15" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="Q15" s="108" t="s">
+      <c r="Q15" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="R15" s="108" t="s">
+      <c r="R15" s="95" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="23.25" thickBot="1">
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="J16" s="110" t="s">
+      <c r="J16" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="K16" s="110" t="s">
+      <c r="K16" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="110" t="s">
+      <c r="L16" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="110" t="s">
+      <c r="M16" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="110" t="s">
+      <c r="N16" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="O16" s="110" t="s">
+      <c r="O16" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="P16" s="110" t="s">
+      <c r="P16" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="Q16" s="110" t="s">
+      <c r="Q16" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="R16" s="110" t="s">
+      <c r="R16" s="97" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="13.5" thickBot="1">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17" t="str">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="str">
         <f>F2&amp;"a"</f>
         <v>M€2005a</v>
       </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17" t="s">
+      <c r="G17" s="14"/>
+      <c r="H17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="110" t="s">
+      <c r="J17" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-    </row>
-    <row r="18" spans="2:18" ht="12.75">
-      <c r="B18" s="25" t="str">
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="22" t="str">
         <f>Sector_Fuels_ELC!L18</f>
         <v>FTE-ELCCOA</v>
       </c>
@@ -5590,44 +5385,44 @@
         <f>RIGHT(D18,3)</f>
         <v>COA</v>
       </c>
-      <c r="D18" s="25" t="str">
+      <c r="D18" s="22" t="str">
         <f>L5</f>
         <v>ELCCOA</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="71">
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="64">
         <v>1</v>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="65">
         <v>30</v>
       </c>
-      <c r="J18" s="115" t="s">
+      <c r="J18" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="K18" s="116"/>
-      <c r="L18" s="111" t="str">
-        <f t="shared" si="1" ref="L18:L25">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+      <c r="K18" s="100"/>
+      <c r="L18" s="94" t="str">
+        <f t="shared" ref="L18:L25" si="1">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-ELCCOA</v>
       </c>
-      <c r="M18" s="112" t="str">
-        <f t="shared" si="2" ref="M18:M25">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+      <c r="M18" s="98" t="str">
+        <f t="shared" ref="M18:M25" si="2">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
-      <c r="N18" s="111" t="str">
-        <f t="shared" si="3" ref="N18:N25">$E$2</f>
+      <c r="N18" s="94" t="str">
+        <f t="shared" ref="N18:N25" si="3">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O18" s="111" t="str">
-        <f t="shared" si="4" ref="O18:O25">$E$2&amp;"a"</f>
+      <c r="O18" s="94" t="str">
+        <f t="shared" ref="O18:O25" si="4">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="111"/>
-    </row>
-    <row r="19" spans="2:18" ht="12.75">
-      <c r="B19" s="25" t="str">
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="22" t="str">
         <f>Sector_Fuels_ELC!L19</f>
         <v>FTE-ELCGAS</v>
       </c>
@@ -5635,42 +5430,42 @@
         <f>RIGHT(D19,3)</f>
         <v>GAS</v>
       </c>
-      <c r="D19" s="25" t="str">
+      <c r="D19" s="22" t="str">
         <f>L6</f>
         <v>ELCGAS</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="71">
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="64">
         <v>1</v>
       </c>
-      <c r="H19" s="72">
+      <c r="H19" s="65">
         <v>30</v>
       </c>
-      <c r="J19" s="113"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="111" t="str">
+      <c r="J19" s="94"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCGAS</v>
       </c>
-      <c r="M19" s="112" t="str">
+      <c r="M19" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
       </c>
-      <c r="N19" s="111" t="str">
+      <c r="N19" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O19" s="111" t="str">
+      <c r="O19" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="111"/>
-    </row>
-    <row r="20" spans="2:18" ht="12.75">
-      <c r="B20" s="25" t="str">
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="22" t="str">
         <f>Sector_Fuels_ELC!L20</f>
         <v>FTE-ELCOIL</v>
       </c>
@@ -5678,153 +5473,153 @@
         <f>'EB1'!G$2</f>
         <v>DSL</v>
       </c>
-      <c r="D20" s="25" t="str">
+      <c r="D20" s="22" t="str">
         <f>L7</f>
         <v>ELCOIL</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="63">
         <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>0.049257354796510562</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="71">
+        <v>4.9257354796510562E-2</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="64">
         <v>1</v>
       </c>
-      <c r="H20" s="72">
+      <c r="H20" s="65">
         <v>30</v>
       </c>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="111" t="str">
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCOIL</v>
       </c>
-      <c r="M20" s="112" t="str">
+      <c r="M20" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants oil</v>
       </c>
-      <c r="N20" s="111" t="str">
+      <c r="N20" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O20" s="111" t="str">
+      <c r="O20" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
-    </row>
-    <row r="21" spans="2:18" ht="12.75">
-      <c r="B21" s="25"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="22"/>
       <c r="C21" t="str">
         <f>'EB1'!I$2</f>
         <v>LPG</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="70">
+      <c r="D21" s="22"/>
+      <c r="E21" s="63">
         <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>0.038926710484734312</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="72"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="111" t="str">
+        <v>3.8926710484734312E-2</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="65"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCNUC</v>
       </c>
-      <c r="M21" s="112" t="str">
+      <c r="M21" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
       </c>
-      <c r="N21" s="111" t="str">
+      <c r="N21" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O21" s="111" t="str">
+      <c r="O21" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P21" s="117"/>
-      <c r="Q21" s="117"/>
-      <c r="R21" s="111"/>
-    </row>
-    <row r="22" spans="2:18" ht="12.75">
-      <c r="B22" s="25"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="22"/>
       <c r="C22" t="str">
         <f>'EB1'!L$2</f>
         <v>HFO</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="70">
+      <c r="D22" s="22"/>
+      <c r="E22" s="63">
         <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>0.85705723214511731</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111" t="str">
+      <c r="F22" s="9"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="65"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCBIO</v>
       </c>
-      <c r="M22" s="112" t="str">
+      <c r="M22" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
       </c>
-      <c r="N22" s="111" t="str">
+      <c r="N22" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O22" s="111" t="str">
+      <c r="O22" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="111"/>
-    </row>
-    <row r="23" spans="2:18" ht="12.75">
-      <c r="B23" s="25"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="22"/>
       <c r="C23" t="str">
         <f>'EB1'!M$2</f>
         <v>OPP</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="70">
+      <c r="D23" s="22"/>
+      <c r="E23" s="63">
         <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>0.054758702573637796</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="72"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113"/>
-      <c r="L23" s="111" t="str">
+        <v>5.4758702573637796E-2</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="65"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCHYD</v>
       </c>
-      <c r="M23" s="112" t="str">
+      <c r="M23" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
       </c>
-      <c r="N23" s="111" t="str">
+      <c r="N23" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O23" s="111" t="str">
+      <c r="O23" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="113"/>
-    </row>
-    <row r="24" spans="2:18" ht="12.75">
-      <c r="B24" s="28" t="str">
+      <c r="P23" s="94"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="22" t="str">
         <f>Sector_Fuels_ELC!L21</f>
         <v>FTE-ELCNUC</v>
       </c>
@@ -5832,42 +5627,42 @@
         <f>RIGHT(D24,3)</f>
         <v>NUC</v>
       </c>
-      <c r="D24" s="25" t="str">
+      <c r="D24" s="22" t="str">
         <f>L8</f>
         <v>ELCNUC</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="71">
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="64">
         <v>1</v>
       </c>
-      <c r="H24" s="72">
+      <c r="H24" s="65">
         <v>30</v>
       </c>
-      <c r="J24" s="113"/>
-      <c r="K24" s="113"/>
-      <c r="L24" s="111" t="str">
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCWIN</v>
       </c>
-      <c r="M24" s="112" t="str">
+      <c r="M24" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
       </c>
-      <c r="N24" s="111" t="str">
+      <c r="N24" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O24" s="111" t="str">
+      <c r="O24" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="113"/>
-    </row>
-    <row r="25" spans="2:18" ht="12.75">
-      <c r="B25" s="28" t="str">
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B25" s="22" t="str">
         <f>Sector_Fuels_ELC!L22</f>
         <v>FTE-ELCBIO</v>
       </c>
@@ -5875,42 +5670,42 @@
         <f>RIGHT(D25,3)</f>
         <v>BIO</v>
       </c>
-      <c r="D25" s="25" t="str">
+      <c r="D25" s="22" t="str">
         <f>L9</f>
         <v>ELCBIO</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="71">
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="64">
         <v>1</v>
       </c>
-      <c r="H25" s="72">
+      <c r="H25" s="65">
         <v>30</v>
       </c>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="111" t="str">
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94" t="str">
         <f t="shared" si="1"/>
         <v>FTE-ELCSOL</v>
       </c>
-      <c r="M25" s="112" t="str">
+      <c r="M25" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
       </c>
-      <c r="N25" s="111" t="str">
+      <c r="N25" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="O25" s="111" t="str">
+      <c r="O25" s="94" t="str">
         <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="113"/>
-    </row>
-    <row r="26" spans="2:8" ht="12.75">
-      <c r="B26" s="28" t="str">
+      <c r="P25" s="94"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" s="22" t="str">
         <f>Sector_Fuels_ELC!L23</f>
         <v>FTE-ELCHYD</v>
       </c>
@@ -5918,21 +5713,21 @@
         <f>RIGHT(D26,3)</f>
         <v>HYD</v>
       </c>
-      <c r="D26" s="25" t="str">
+      <c r="D26" s="22" t="str">
         <f>L10</f>
         <v>ELCHYD</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="71">
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="64">
         <v>1</v>
       </c>
-      <c r="H26" s="72">
+      <c r="H26" s="65">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="12.75">
-      <c r="B27" s="28" t="str">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B27" s="22" t="str">
         <f>Sector_Fuels_ELC!L24</f>
         <v>FTE-ELCWIN</v>
       </c>
@@ -5940,21 +5735,21 @@
         <f>RIGHT(D27,3)</f>
         <v>WIN</v>
       </c>
-      <c r="D27" s="25" t="str">
+      <c r="D27" s="22" t="str">
         <f>L11</f>
         <v>ELCWIN</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="71">
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="64">
         <v>1</v>
       </c>
-      <c r="H27" s="72">
+      <c r="H27" s="65">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="12.75">
-      <c r="B28" s="28" t="str">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B28" s="22" t="str">
         <f>Sector_Fuels_ELC!L25</f>
         <v>FTE-ELCSOL</v>
       </c>
@@ -5962,1226 +5757,1192 @@
         <f>RIGHT(D28,3)</f>
         <v>SOL</v>
       </c>
-      <c r="D28" s="25" t="str">
+      <c r="D28" s="22" t="str">
         <f>L12</f>
         <v>ELCSOL</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="71">
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="64">
         <v>1</v>
       </c>
-      <c r="H28" s="72">
+      <c r="H28" s="65">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="12.75">
-      <c r="B32" s="52"/>
-      <c r="C32" s="1" t="s">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B32" s="45"/>
+      <c r="C32" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="12.75">
-      <c r="B33" s="68"/>
-      <c r="C33" s="1" t="s">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="61"/>
+      <c r="C33" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:AB65536"/>
-  <sheetFormatPr defaultColWidth="8.85428571428571" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="16.4285714285714" style="25" customWidth="1"/>
-    <col min="3" max="3" width="12.1428571428571" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.2857142857143" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.14285714285714" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85714285714286" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.2857142857143" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5714285714286" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.14285714285714" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.4285714285714" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.42857142857143" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="43.2857142857143" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28571428571429" customWidth="1"/>
-    <col min="25" max="25" width="11.4285714285714" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="22" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="22" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2" style="22" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.14285714285714" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.85714285714286" style="25"/>
+    <col min="28" max="28" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.85546875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="30">
-      <c r="B1" s="24" t="s">
+    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="31.5">
-      <c r="B2" s="14" t="str">
+    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
       </c>
-      <c r="C2" s="22" t="str">
+      <c r="C2" s="19" t="str">
         <f>'EB1'!C6</f>
         <v>Electricity Plants</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="12" t="str">
         <f>'EB1'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="14" t="str">
+      <c r="G2" s="12" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="106" t="s">
+      <c r="T2" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="106"/>
-      <c r="V2" s="107"/>
-      <c r="W2" s="107"/>
-      <c r="X2" s="107"/>
-      <c r="Y2" s="107"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="107"/>
-      <c r="AB2" s="107"/>
-    </row>
-    <row r="3" spans="20:28" ht="12.75">
-      <c r="T3" s="108" t="s">
+      <c r="U2" s="93"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="94"/>
+      <c r="AB2" s="94"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="T3" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="109" t="s">
+      <c r="U3" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="108" t="s">
+      <c r="V3" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="W3" s="108" t="s">
+      <c r="W3" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="X3" s="108" t="s">
+      <c r="X3" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="108" t="s">
+      <c r="Y3" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="108" t="s">
+      <c r="Z3" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="108" t="s">
+      <c r="AA3" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="108" t="s">
+      <c r="AB3" s="95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" s="26" customFormat="1" ht="30.75" thickBot="1">
-      <c r="B4" s="33" t="s">
+    <row r="4" spans="2:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="110" t="s">
+      <c r="H4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="T4" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="110" t="s">
+      <c r="U4" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="110" t="s">
+      <c r="W4" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="110" t="s">
+      <c r="X4" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="110" t="s">
+      <c r="Y4" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" s="110" t="s">
+      <c r="Z4" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" s="110" t="s">
+      <c r="AA4" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="110" t="s">
+      <c r="AB4" s="97" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" s="26" customFormat="1" ht="15.75">
-      <c r="B5" s="32" t="s">
+    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="115" t="s">
+      <c r="H5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="T5" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="111"/>
-      <c r="V5" s="115" t="str">
+      <c r="U5" s="94"/>
+      <c r="V5" s="94" t="str">
         <f>'EB1'!$U$2</f>
         <v>ELC</v>
       </c>
-      <c r="W5" s="115" t="str">
+      <c r="W5" s="94" t="str">
         <f>'EB1'!$U$3</f>
         <v>Electricity</v>
       </c>
-      <c r="X5" s="115" t="str">
+      <c r="X5" s="94" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Y5" s="115"/>
-      <c r="Z5" s="115" t="s">
+      <c r="Y5" s="94"/>
+      <c r="Z5" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115" t="s">
+      <c r="AA5" s="94"/>
+      <c r="AB5" s="94" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="20:28" ht="12.75">
-      <c r="T6" s="113" t="s">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="T6" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="U6" s="113"/>
-      <c r="V6" s="113" t="str">
+      <c r="U6" s="94"/>
+      <c r="V6" s="94" t="str">
         <f>$B$2&amp;'EB1'!$C$15</f>
         <v>ELCCO2</v>
       </c>
-      <c r="W6" s="113" t="str">
+      <c r="W6" s="94" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$16</f>
         <v>Electricity Plants Carbon dioxide</v>
       </c>
-      <c r="X6" s="113" t="str">
+      <c r="X6" s="94" t="str">
         <f>'EB1'!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="113"/>
-      <c r="AB6" s="113"/>
-    </row>
-    <row r="7" spans="20:21" ht="12.75">
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" spans="4:28" ht="12.75">
-      <c r="D8" s="4" t="s">
+      <c r="Y6" s="94"/>
+      <c r="Z6" s="94"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="94"/>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="3"/>
-      <c r="Q8" s="26"/>
-      <c r="T8" s="106" t="s">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="T8" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="106"/>
-      <c r="V8" s="107"/>
-      <c r="W8" s="107"/>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="107"/>
-      <c r="Z8" s="107"/>
-      <c r="AA8" s="107"/>
-      <c r="AB8" s="107"/>
-    </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1">
-      <c r="B9" s="21" t="s">
+      <c r="U8" s="93"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="94"/>
+      <c r="X8" s="94"/>
+      <c r="Y8" s="94"/>
+      <c r="Z8" s="94"/>
+      <c r="AA8" s="94"/>
+      <c r="AB8" s="94"/>
+    </row>
+    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="72" t="s">
         <v>148</v>
       </c>
-      <c r="I9" s="80" t="s">
+      <c r="I9" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="80" t="s">
+      <c r="J9" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="K9" s="80" t="s">
+      <c r="K9" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="L9" s="80" t="s">
+      <c r="L9" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="80" t="s">
+      <c r="M9" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="80" t="s">
+      <c r="N9" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="80" t="s">
+      <c r="O9" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="P9" s="80" t="s">
+      <c r="P9" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="101" t="s">
+      <c r="Q9" s="24"/>
+      <c r="R9" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="108" t="s">
+      <c r="S9" s="28"/>
+      <c r="T9" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="109" t="s">
+      <c r="U9" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="108" t="s">
+      <c r="V9" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="W9" s="108" t="s">
+      <c r="W9" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="X9" s="108" t="s">
+      <c r="X9" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="Y9" s="108" t="s">
+      <c r="Y9" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="108" t="s">
+      <c r="Z9" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="AA9" s="108" t="s">
+      <c r="AA9" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" s="108" t="s">
+      <c r="AB9" s="95" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="23.25" thickBot="1">
-      <c r="B10" s="19" t="s">
+    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="86" t="s">
+      <c r="H10" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="86" t="s">
+      <c r="J10" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="38" t="s">
+      <c r="R10" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="S10" s="36"/>
-      <c r="T10" s="110" t="s">
+      <c r="S10" s="29"/>
+      <c r="T10" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="110" t="s">
+      <c r="U10" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="110" t="s">
+      <c r="V10" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="W10" s="110" t="s">
+      <c r="W10" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="X10" s="110" t="s">
+      <c r="X10" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="Y10" s="110" t="s">
+      <c r="Y10" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="110" t="s">
+      <c r="Z10" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="AA10" s="110" t="s">
+      <c r="AA10" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="AB10" s="110" t="s">
+      <c r="AB10" s="97" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="13.5" thickBot="1">
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="105" t="str">
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="14" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="F11" s="105" t="str">
+      <c r="F11" s="14" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="G11" s="17" t="str">
+      <c r="G11" s="14" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="H11" s="81" t="str">
+      <c r="H11" s="73" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="17" t="str">
+      <c r="I11" s="14"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="14" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2005/GW</v>
       </c>
-      <c r="L11" s="17" t="str">
+      <c r="L11" s="14" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2005/GW</v>
       </c>
-      <c r="M11" s="17" t="str">
+      <c r="M11" s="14" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2005/PJ</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="17" t="str">
+      <c r="O11" s="14" t="str">
         <f>$E$2&amp;"/"&amp;$F$2</f>
         <v>PJ/GW</v>
       </c>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="102" t="s">
+      <c r="P11" s="14"/>
+      <c r="R11" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="S11" s="36"/>
-      <c r="T11" s="110" t="s">
+      <c r="S11" s="29"/>
+      <c r="T11" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
-      <c r="AB11" s="110"/>
-    </row>
-    <row r="12" spans="2:28" ht="12.75">
-      <c r="B12" s="25" t="str">
-        <f t="shared" si="0" ref="B12:B19">V12</f>
+      <c r="U11" s="97"/>
+      <c r="V11" s="97"/>
+      <c r="W11" s="97"/>
+      <c r="X11" s="97"/>
+      <c r="Y11" s="97"/>
+      <c r="Z11" s="97"/>
+      <c r="AA11" s="97"/>
+      <c r="AB11" s="97"/>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B12" s="22" t="str">
+        <f t="shared" ref="B12:B19" si="0">V12</f>
         <v>ELCTECOA00</v>
       </c>
-      <c r="C12" s="25" t="str">
+      <c r="C12" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L5,3)</f>
         <v>ELCCOA</v>
       </c>
-      <c r="D12" s="25" t="str">
-        <f t="shared" si="1" ref="D12:D19">$V$5</f>
+      <c r="D12" s="22" t="str">
+        <f t="shared" ref="D12:D19" si="1">$V$5</f>
         <v>ELC</v>
       </c>
-      <c r="G12" s="98">
+      <c r="G12" s="87">
         <f>(-'EB1'!$D$6*$I$12)/($J$12*$O$12)</f>
         <v>89.372771062763022</v>
       </c>
-      <c r="H12" s="69"/>
-      <c r="I12" s="76">
+      <c r="H12" s="62"/>
+      <c r="I12" s="68">
         <v>0.38400000000000001</v>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="68">
         <v>0.85</v>
       </c>
-      <c r="K12" s="75"/>
-      <c r="L12" s="76">
+      <c r="K12" s="67"/>
+      <c r="L12" s="68">
         <v>40</v>
       </c>
-      <c r="M12" s="76">
-        <v>0.50</v>
-      </c>
-      <c r="N12" s="75">
+      <c r="M12" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="67">
         <v>30</v>
       </c>
-      <c r="O12" s="75">
+      <c r="O12" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="68">
         <v>1</v>
       </c>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="34">
-        <f t="shared" si="2" ref="R12:R19">G12*$J12*$O12</f>
+      <c r="R12" s="27">
+        <f t="shared" ref="R12:R19" si="2">G12*$J12*$O12</f>
         <v>2395.6907520000004</v>
       </c>
-      <c r="S12" s="100"/>
-      <c r="T12" s="111" t="s">
+      <c r="S12" s="88"/>
+      <c r="T12" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="U12" s="111"/>
-      <c r="V12" s="111" t="str">
+      <c r="U12" s="94"/>
+      <c r="V12" s="94" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$5,3)&amp;"00"</f>
         <v>ELCTECOA00</v>
       </c>
-      <c r="W12" s="112" t="str">
+      <c r="W12" s="98" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V12,2)&amp;" - "&amp;'EB1'!D3</f>
         <v>Power Plants Existing00 - Solid Fuels</v>
       </c>
-      <c r="X12" s="111" t="str">
-        <f t="shared" si="3" ref="X12:X19">$E$2</f>
+      <c r="X12" s="94" t="str">
+        <f t="shared" ref="X12:X19" si="3">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Y12" s="111" t="str">
-        <f t="shared" si="4" ref="Y12:Y19">$F$2</f>
+      <c r="Y12" s="94" t="str">
+        <f t="shared" ref="Y12:Y19" si="4">$F$2</f>
         <v>GW</v>
       </c>
-      <c r="Z12" s="115" t="s">
+      <c r="Z12" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="AA12" s="111"/>
-      <c r="AB12" s="111"/>
-    </row>
-    <row r="13" spans="2:28" ht="12.75">
-      <c r="B13" s="25" t="str">
+      <c r="AA12" s="94"/>
+      <c r="AB12" s="94"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B13" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCTEGAS00</v>
       </c>
-      <c r="C13" s="25" t="str">
+      <c r="C13" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L6,3)</f>
         <v>ELCGAS</v>
       </c>
-      <c r="D13" s="25" t="str">
+      <c r="D13" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="G13" s="98">
+      <c r="G13" s="87">
         <f>(-'EB1'!$E$6*$I$13)/($J$13*$O$13)</f>
         <v>41.450437783149788</v>
       </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="94">
+      <c r="H13" s="62"/>
+      <c r="I13" s="68">
         <v>0.4929</v>
       </c>
-      <c r="J13" s="76">
+      <c r="J13" s="68">
         <v>0.85</v>
       </c>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76">
+      <c r="K13" s="67"/>
+      <c r="L13" s="68">
         <v>35</v>
       </c>
-      <c r="M13" s="76">
-        <v>0.40</v>
-      </c>
-      <c r="N13" s="75">
+      <c r="M13" s="68">
+        <v>0.4</v>
+      </c>
+      <c r="N13" s="67">
         <v>20</v>
       </c>
-      <c r="O13" s="75">
+      <c r="O13" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="68">
         <v>1</v>
       </c>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="34">
+      <c r="R13" s="27">
         <f t="shared" si="2"/>
         <v>1111.1038550399999</v>
       </c>
-      <c r="S13" s="37"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="111"/>
-      <c r="V13" s="111" t="str">
+      <c r="S13" s="30"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"00"</f>
         <v>ELCTEGAS00</v>
       </c>
-      <c r="W13" s="112" t="str">
+      <c r="W13" s="98" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V13,2)&amp;" - "&amp;'EB1'!E3</f>
         <v>Power Plants Existing00 - Natural Gas</v>
       </c>
-      <c r="X13" s="111" t="str">
+      <c r="X13" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y13" s="111" t="str">
+      <c r="Y13" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z13" s="111"/>
-      <c r="AA13" s="111"/>
-      <c r="AB13" s="111"/>
-    </row>
-    <row r="14" spans="2:28" ht="12.75">
-      <c r="B14" s="25" t="str">
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="94"/>
+      <c r="AB13" s="94"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B14" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCTEOIL00</v>
       </c>
-      <c r="C14" s="25" t="str">
+      <c r="C14" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L7,3)</f>
         <v>ELCOIL</v>
       </c>
-      <c r="D14" s="25" t="str">
+      <c r="D14" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="G14" s="98">
+      <c r="G14" s="87">
         <f>((-SUM('EB1'!G6:M6)*$I$14)/($J$14*$O$14))</f>
         <v>5.710602448742053</v>
       </c>
-      <c r="H14" s="69"/>
-      <c r="I14" s="94">
+      <c r="H14" s="62"/>
+      <c r="I14" s="68">
         <v>0.25</v>
       </c>
-      <c r="J14" s="94">
+      <c r="J14" s="68">
         <v>0.85</v>
       </c>
-      <c r="K14" s="93"/>
-      <c r="L14" s="94">
+      <c r="K14" s="67"/>
+      <c r="L14" s="68">
         <v>20</v>
       </c>
-      <c r="M14" s="94">
-        <v>0.20</v>
-      </c>
-      <c r="N14" s="93">
+      <c r="M14" s="68">
+        <v>0.2</v>
+      </c>
+      <c r="N14" s="67">
         <v>30</v>
       </c>
-      <c r="O14" s="75">
+      <c r="O14" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="68">
         <v>1</v>
       </c>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="34">
+      <c r="R14" s="27">
         <f t="shared" si="2"/>
         <v>153.07612499999996</v>
       </c>
-      <c r="S14" s="37"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111" t="str">
+      <c r="S14" s="30"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$7,3)&amp;"00"</f>
         <v>ELCTEOIL00</v>
       </c>
-      <c r="W14" s="112" t="str">
+      <c r="W14" s="98" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V14,2)&amp;" - "&amp;'EB1'!F3</f>
         <v>Power Plants Existing00 - Crude oil</v>
       </c>
-      <c r="X14" s="111" t="str">
+      <c r="X14" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y14" s="111" t="str">
+      <c r="Y14" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z14" s="111"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="111"/>
-    </row>
-    <row r="15" spans="2:28" ht="12.75">
-      <c r="B15" s="28" t="str">
+      <c r="Z14" s="94"/>
+      <c r="AA14" s="94"/>
+      <c r="AB14" s="94"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCNENUC00</v>
       </c>
-      <c r="C15" s="25" t="str">
+      <c r="C15" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L8,3)</f>
         <v>ELCNUC</v>
       </c>
-      <c r="D15" s="28" t="str">
+      <c r="D15" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="99">
+      <c r="G15" s="87">
         <f>(-'EB1'!$N$6*$I$15)/($J$15*$O$15)</f>
         <v>51.797945205479458</v>
       </c>
-      <c r="H15" s="99">
+      <c r="H15" s="87">
         <f>G15</f>
         <v>51.797945205479458</v>
       </c>
-      <c r="I15" s="93">
+      <c r="I15" s="67">
         <v>0.33</v>
       </c>
-      <c r="J15" s="94">
-        <v>0.90</v>
-      </c>
-      <c r="K15" s="93"/>
-      <c r="L15" s="94">
+      <c r="J15" s="68">
+        <v>0.9</v>
+      </c>
+      <c r="K15" s="67"/>
+      <c r="L15" s="68">
         <v>38</v>
       </c>
-      <c r="M15" s="93">
+      <c r="M15" s="67">
         <v>0.27</v>
       </c>
-      <c r="N15" s="74"/>
-      <c r="O15" s="93">
+      <c r="N15" s="44"/>
+      <c r="O15" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P15" s="94">
+      <c r="P15" s="68">
         <v>1</v>
       </c>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="34">
+      <c r="R15" s="27">
         <f t="shared" si="2"/>
         <v>1470.1500000000003</v>
       </c>
-      <c r="S15" s="37"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111" t="str">
+      <c r="S15" s="30"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94" t="str">
         <f>$B$2&amp;$F$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$8,3)&amp;"00"</f>
         <v>ELCNENUC00</v>
       </c>
-      <c r="W15" s="118" t="str">
+      <c r="W15" s="94" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V15,2)&amp;" - "&amp;'EB1'!N3</f>
         <v>Power Plants Existing00 - Nuclear Energy</v>
       </c>
-      <c r="X15" s="111" t="str">
+      <c r="X15" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y15" s="111" t="str">
+      <c r="Y15" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z15" s="115" t="s">
+      <c r="Z15" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="AA15" s="111"/>
-      <c r="AB15" s="111"/>
-    </row>
-    <row r="16" spans="2:28" ht="12.75">
-      <c r="B16" s="28" t="str">
+      <c r="AA15" s="94"/>
+      <c r="AB15" s="94"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B16" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCREBIO00</v>
       </c>
-      <c r="C16" s="25" t="str">
+      <c r="C16" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D16" s="28" t="str">
+      <c r="D16" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="99">
+      <c r="G16" s="87">
         <f>(-'EB1'!$O$6*$I$16)/($J$16*$O$16)</f>
         <v>7.8023302733384083</v>
       </c>
-      <c r="H16" s="92"/>
-      <c r="I16" s="73">
+      <c r="H16" s="62"/>
+      <c r="I16" s="66">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J16" s="73">
-        <v>0.60</v>
-      </c>
-      <c r="K16" s="73"/>
-      <c r="L16" s="74">
+      <c r="J16" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="K16" s="66"/>
+      <c r="L16" s="44">
         <v>25</v>
       </c>
-      <c r="M16" s="73">
+      <c r="M16" s="66">
         <v>0.35</v>
       </c>
-      <c r="N16" s="74">
+      <c r="N16" s="44">
         <v>25</v>
       </c>
-      <c r="O16" s="93">
+      <c r="O16" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P16" s="94">
+      <c r="P16" s="68">
         <v>1</v>
       </c>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="34">
+      <c r="R16" s="27">
         <f t="shared" si="2"/>
         <v>147.63257250000001</v>
       </c>
-      <c r="S16" s="37"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111" t="str">
+      <c r="S16" s="30"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"00"</f>
         <v>ELCREBIO00</v>
       </c>
-      <c r="W16" s="118" t="str">
+      <c r="W16" s="94" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V16,2)&amp;" - "&amp;'EB1'!O3</f>
         <v>Power Plants Existing00 - Biomass</v>
       </c>
-      <c r="X16" s="111" t="str">
+      <c r="X16" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y16" s="111" t="str">
+      <c r="Y16" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-    </row>
-    <row r="17" spans="2:28" ht="12.75">
-      <c r="B17" s="28" t="str">
+      <c r="Z16" s="94"/>
+      <c r="AA16" s="94"/>
+      <c r="AB16" s="94"/>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B17" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCREHYD00</v>
       </c>
-      <c r="C17" s="25" t="str">
+      <c r="C17" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L10,3)</f>
         <v>ELCHYD</v>
       </c>
-      <c r="D17" s="28" t="str">
+      <c r="D17" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="44">
         <v>15</v>
       </c>
-      <c r="F17" s="74">
+      <c r="F17" s="44">
         <v>16</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="73">
+      <c r="G17" s="91"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="66">
         <v>1</v>
       </c>
-      <c r="J17" s="73">
-        <v>0.50</v>
-      </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="74">
+      <c r="J17" s="66">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="66"/>
+      <c r="L17" s="44">
         <v>50</v>
       </c>
-      <c r="M17" s="73">
+      <c r="M17" s="66">
         <v>2</v>
       </c>
-      <c r="N17" s="74">
+      <c r="N17" s="44">
         <v>50</v>
       </c>
-      <c r="O17" s="93">
+      <c r="O17" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P17" s="94">
-        <v>0.50</v>
-      </c>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="34">
+      <c r="P17" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="27">
         <f>(E17+F17)*$J17*$O17</f>
         <v>488.80799999999999</v>
       </c>
-      <c r="S17" s="37"/>
-      <c r="T17" s="111"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="111" t="str">
+      <c r="S17" s="30"/>
+      <c r="T17" s="94"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="94" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
         <v>ELCREHYD00</v>
       </c>
-      <c r="W17" s="118" t="str">
+      <c r="W17" s="94" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V17,2)&amp;" - "&amp;'EB1'!P3</f>
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
-      <c r="X17" s="111" t="str">
+      <c r="X17" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y17" s="111" t="str">
+      <c r="Y17" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z17" s="111"/>
-      <c r="AA17" s="111"/>
-      <c r="AB17" s="111"/>
-    </row>
-    <row r="18" spans="2:28" ht="12.75">
-      <c r="B18" s="28" t="str">
+      <c r="Z17" s="94"/>
+      <c r="AA17" s="94"/>
+      <c r="AB17" s="94"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B18" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCREWIN00</v>
       </c>
-      <c r="C18" s="25" t="str">
+      <c r="C18" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L11,3)</f>
         <v>ELCWIN</v>
       </c>
-      <c r="D18" s="28" t="str">
+      <c r="D18" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="99">
+      <c r="G18" s="87">
         <f>(-'EB1'!$Q$6*$I$18)/($J$18*$O$18)</f>
         <v>23.908866057838662</v>
       </c>
-      <c r="H18" s="92"/>
-      <c r="I18" s="73">
+      <c r="H18" s="62"/>
+      <c r="I18" s="66">
         <v>1</v>
       </c>
-      <c r="J18" s="73">
+      <c r="J18" s="66">
         <v>0.35</v>
       </c>
-      <c r="K18" s="73"/>
-      <c r="L18" s="74">
+      <c r="K18" s="66"/>
+      <c r="L18" s="44">
         <v>35</v>
       </c>
-      <c r="M18" s="73">
-        <v>0.50</v>
-      </c>
-      <c r="N18" s="74">
+      <c r="M18" s="66">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="44">
         <v>20</v>
       </c>
-      <c r="O18" s="93">
+      <c r="O18" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P18" s="94">
-        <v>0.30</v>
-      </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="34">
+      <c r="P18" s="68">
+        <v>0.3</v>
+      </c>
+      <c r="R18" s="27">
         <f t="shared" si="2"/>
         <v>263.8965</v>
       </c>
-      <c r="S18" s="37"/>
-      <c r="T18" s="111"/>
-      <c r="U18" s="111"/>
-      <c r="V18" s="111" t="str">
+      <c r="S18" s="30"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$11,3)&amp;"00"</f>
         <v>ELCREWIN00</v>
       </c>
-      <c r="W18" s="118" t="str">
+      <c r="W18" s="94" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" - "&amp;'EB1'!Q3</f>
         <v>Power Plants Existing00 - Wind energy</v>
       </c>
-      <c r="X18" s="111" t="str">
+      <c r="X18" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y18" s="111" t="str">
+      <c r="Y18" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z18" s="111"/>
-      <c r="AA18" s="111"/>
-      <c r="AB18" s="111"/>
-    </row>
-    <row r="19" spans="2:28" ht="12.75">
-      <c r="B19" s="28" t="str">
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="94"/>
+      <c r="AB18" s="94"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B19" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ELCRESOL00</v>
       </c>
-      <c r="C19" s="25" t="str">
+      <c r="C19" s="22" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
         <v>ELCSOL</v>
       </c>
-      <c r="D19" s="28" t="str">
+      <c r="D19" s="22" t="str">
         <f t="shared" si="1"/>
         <v>ELC</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="99">
+      <c r="G19" s="87">
         <f>(-'EB1'!$R$6*$I$19)/($J$19*$O$19)</f>
         <v>7.1875528496533061</v>
       </c>
-      <c r="H19" s="92"/>
-      <c r="I19" s="73">
+      <c r="H19" s="62"/>
+      <c r="I19" s="66">
         <v>1</v>
       </c>
-      <c r="J19" s="73">
-        <v>0.30</v>
-      </c>
-      <c r="K19" s="73"/>
-      <c r="L19" s="74">
+      <c r="J19" s="66">
+        <v>0.3</v>
+      </c>
+      <c r="K19" s="66"/>
+      <c r="L19" s="44">
         <v>60</v>
       </c>
-      <c r="M19" s="73"/>
-      <c r="N19" s="74">
+      <c r="M19" s="66"/>
+      <c r="N19" s="44">
         <v>15</v>
       </c>
-      <c r="O19" s="93">
+      <c r="O19" s="67">
         <v>31.536000000000001</v>
       </c>
-      <c r="P19" s="94">
-        <v>0.20</v>
-      </c>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="34">
+      <c r="P19" s="68">
+        <v>0.2</v>
+      </c>
+      <c r="R19" s="27">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="S19" s="37"/>
-      <c r="T19" s="111"/>
-      <c r="U19" s="111"/>
-      <c r="V19" s="111" t="str">
+      <c r="S19" s="30"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="94" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"00"</f>
         <v>ELCRESOL00</v>
       </c>
-      <c r="W19" s="118" t="str">
+      <c r="W19" s="94" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" - "&amp;'EB1'!R3</f>
         <v>Power Plants Existing00 - Solar energy</v>
       </c>
-      <c r="X19" s="111" t="str">
+      <c r="X19" s="94" t="str">
         <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
-      <c r="Y19" s="111" t="str">
+      <c r="Y19" s="94" t="str">
         <f t="shared" si="4"/>
         <v>GW</v>
       </c>
-      <c r="Z19" s="111"/>
-      <c r="AA19" s="111"/>
-      <c r="AB19" s="111"/>
-    </row>
-    <row r="21" spans="18:18" ht="12.75">
-      <c r="R21" s="97"/>
-    </row>
-    <row r="22" spans="18:18" ht="12.75">
-      <c r="R22" s="97"/>
-    </row>
-    <row r="23" spans="2:18" ht="12.75">
-      <c r="B23" s="52"/>
-      <c r="C23" s="1" t="s">
+      <c r="Z19" s="94"/>
+      <c r="AA19" s="94"/>
+      <c r="AB19" s="94"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="R21" s="86"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="R22" s="86"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B23" s="45"/>
+      <c r="C23" t="s">
         <v>144</v>
       </c>
-      <c r="R23" s="97"/>
-    </row>
-    <row r="24" spans="2:18" ht="12.75">
-      <c r="B24" s="68"/>
-      <c r="C24" s="1" t="s">
+      <c r="R23" s="86"/>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B24" s="61"/>
+      <c r="C24" t="s">
         <v>145</v>
       </c>
-      <c r="R24" s="97"/>
-    </row>
-    <row r="25" spans="18:18" ht="12.75">
-      <c r="R25" s="97"/>
-    </row>
-    <row r="65536" spans="19:19" ht="12.75">
-      <c r="S65536" s="37"/>
+      <c r="R24" s="86"/>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="R25" s="86"/>
+    </row>
+    <row r="65536" spans="19:19" x14ac:dyDescent="0.2">
+      <c r="S65536" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.45" customHeight="1">
-      <c r="B3" s="42" t="s">
+    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-    </row>
-    <row r="4" spans="2:7" s="6" customFormat="1" ht="17.45" customHeight="1">
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-    </row>
-    <row r="5" spans="2:7" ht="18">
-      <c r="B5" s="40" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="B5" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" spans="2:8" ht="13.5" thickBot="1">
-      <c r="B6" s="45" t="s">
+      <c r="C5" s="34"/>
+    </row>
+    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="45" t="str">
+      <c r="C6" s="38" t="str">
         <f>Sector_Fuels_ELC!$L$5</f>
         <v>ELCCOA</v>
       </c>
-      <c r="D6" s="45" t="str">
+      <c r="D6" s="38" t="str">
         <f>Sector_Fuels_ELC!$L$6</f>
         <v>ELCGAS</v>
       </c>
-      <c r="E6" s="45" t="str">
+      <c r="E6" s="38" t="str">
         <f>Sector_Fuels_ELC!$L$7</f>
         <v>ELCOIL</v>
       </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="2:8" ht="13.5" thickBot="1">
-      <c r="B7" s="18" t="s">
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" ht="12.75">
-      <c r="B8" s="25" t="str">
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="22" t="str">
         <f>Con_ELC!$V$6</f>
         <v>ELCCO2</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="66">
         <v>95</v>
       </c>
-      <c r="D8" s="73">
-        <v>56.10</v>
-      </c>
-      <c r="E8" s="73">
+      <c r="D8" s="66">
+        <v>56.1</v>
+      </c>
+      <c r="E8" s="66">
         <v>76.400000000000006</v>
       </c>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="6:7" ht="12.75">
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="6:7" ht="12.75">
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-    </row>
-    <row r="23" spans="2:3" ht="12.75">
-      <c r="B23" s="52"/>
-      <c r="C23" s="1" t="s">
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" s="45"/>
+      <c r="C23" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="12.75">
-      <c r="B24" s="68"/>
-      <c r="C24" s="1" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="61"/>
+      <c r="C24" t="s">
         <v>145</v>
       </c>
     </row>
